--- a/AAII_Financials/Quarterly/SNTW_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SNTW_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="92">
   <si>
     <t>SNTW</t>
   </si>
@@ -656,137 +656,144 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44135</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44043</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>43951</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43861</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43769</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43677</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43585</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43496</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43404</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43312</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43220</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43131</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43039</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>42947</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>42855</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42766</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42674</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42582</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -874,8 +881,14 @@
       <c r="AE8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -951,11 +964,11 @@
       <c r="AA9" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB9" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC9" s="3">
-        <v>0</v>
+      <c r="AB9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC9" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AD9" s="3">
         <v>0</v>
@@ -963,8 +976,14 @@
       <c r="AE9" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF9" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG9" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1040,11 +1059,11 @@
       <c r="AA10" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB10" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC10" s="3">
-        <v>0</v>
+      <c r="AB10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC10" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AD10" s="3">
         <v>0</v>
@@ -1052,8 +1071,14 @@
       <c r="AE10" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG10" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1085,8 +1110,10 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1174,8 +1201,14 @@
       <c r="AE12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1263,79 +1296,85 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>4</v>
+      <c r="E14" s="3">
+        <v>-200</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
+      <c r="G14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>4</v>
+      <c r="I14" s="3">
+        <v>0</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M14" s="3">
         <v>-100</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
-      <c r="S14" s="3">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>300</v>
       </c>
-      <c r="T14" s="3">
+      <c r="V14" s="3">
         <v>-300</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W14" s="3" t="s">
         <v>4</v>
       </c>
       <c r="X14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="3">
-        <v>0</v>
+      <c r="Y14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA14" s="3">
         <v>0</v>
@@ -1352,8 +1391,14 @@
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1441,8 +1486,14 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1471,86 +1522,88 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E17" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F17" s="3">
+        <v>0</v>
+      </c>
+      <c r="G17" s="3">
         <v>100</v>
       </c>
-      <c r="F17" s="3">
-        <v>0</v>
-      </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
+        <v>0</v>
+      </c>
+      <c r="I17" s="3">
         <v>-100</v>
       </c>
-      <c r="H17" s="3">
-        <v>0</v>
-      </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
+        <v>0</v>
+      </c>
+      <c r="K17" s="3">
         <v>100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>100</v>
       </c>
-      <c r="K17" s="3">
-        <v>0</v>
-      </c>
-      <c r="L17" s="3">
-        <v>0</v>
-      </c>
       <c r="M17" s="3">
+        <v>0</v>
+      </c>
+      <c r="N17" s="3">
+        <v>0</v>
+      </c>
+      <c r="O17" s="3">
         <v>300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>100</v>
       </c>
-      <c r="P17" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="3">
-        <v>0</v>
-      </c>
       <c r="R17" s="3">
         <v>0</v>
       </c>
       <c r="S17" s="3">
+        <v>0</v>
+      </c>
+      <c r="T17" s="3">
+        <v>0</v>
+      </c>
+      <c r="U17" s="3">
         <v>400</v>
       </c>
-      <c r="T17" s="3">
-        <v>0</v>
-      </c>
-      <c r="U17" s="3">
-        <v>0</v>
-      </c>
       <c r="V17" s="3">
+        <v>0</v>
+      </c>
+      <c r="W17" s="3">
+        <v>0</v>
+      </c>
+      <c r="X17" s="3">
         <v>200</v>
       </c>
-      <c r="W17" s="3">
-        <v>0</v>
-      </c>
-      <c r="X17" s="3">
-        <v>0</v>
-      </c>
       <c r="Y17" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z17" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA17" s="3">
         <v>100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>100</v>
       </c>
-      <c r="AA17" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB17" s="3">
-        <v>0</v>
-      </c>
       <c r="AC17" s="3">
         <v>0</v>
       </c>
@@ -1560,8 +1613,14 @@
       <c r="AE17" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF17" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1569,77 +1628,77 @@
         <v>4</v>
       </c>
       <c r="E18" s="3">
+        <v>100</v>
+      </c>
+      <c r="F18" s="3">
+        <v>0</v>
+      </c>
+      <c r="G18" s="3">
         <v>-100</v>
       </c>
-      <c r="F18" s="3">
-        <v>0</v>
-      </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
+        <v>0</v>
+      </c>
+      <c r="I18" s="3">
         <v>100</v>
       </c>
-      <c r="H18" s="3">
-        <v>0</v>
-      </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
+        <v>0</v>
+      </c>
+      <c r="K18" s="3">
         <v>-100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-100</v>
       </c>
-      <c r="K18" s="3">
-        <v>0</v>
-      </c>
-      <c r="L18" s="3">
-        <v>0</v>
-      </c>
       <c r="M18" s="3">
+        <v>0</v>
+      </c>
+      <c r="N18" s="3">
+        <v>0</v>
+      </c>
+      <c r="O18" s="3">
         <v>-300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-100</v>
       </c>
-      <c r="P18" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>0</v>
-      </c>
       <c r="R18" s="3">
         <v>0</v>
       </c>
       <c r="S18" s="3">
+        <v>0</v>
+      </c>
+      <c r="T18" s="3">
+        <v>0</v>
+      </c>
+      <c r="U18" s="3">
         <v>-400</v>
       </c>
-      <c r="T18" s="3">
-        <v>0</v>
-      </c>
-      <c r="U18" s="3">
-        <v>0</v>
-      </c>
       <c r="V18" s="3">
+        <v>0</v>
+      </c>
+      <c r="W18" s="3">
+        <v>0</v>
+      </c>
+      <c r="X18" s="3">
         <v>-200</v>
       </c>
-      <c r="W18" s="3">
-        <v>0</v>
-      </c>
-      <c r="X18" s="3">
-        <v>0</v>
-      </c>
       <c r="Y18" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="3">
         <v>-100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-100</v>
       </c>
-      <c r="AA18" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB18" s="3">
-        <v>0</v>
-      </c>
       <c r="AC18" s="3">
         <v>0</v>
       </c>
@@ -1649,8 +1708,14 @@
       <c r="AE18" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1682,8 +1747,10 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1771,8 +1838,14 @@
       <c r="AE20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1780,34 +1853,34 @@
         <v>4</v>
       </c>
       <c r="E21" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F21" s="3">
         <v>0</v>
       </c>
       <c r="G21" s="3">
+        <v>0</v>
+      </c>
+      <c r="H21" s="3">
+        <v>0</v>
+      </c>
+      <c r="I21" s="3">
         <v>100</v>
       </c>
-      <c r="H21" s="3">
-        <v>0</v>
-      </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
+        <v>0</v>
+      </c>
+      <c r="K21" s="3">
         <v>-100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-100</v>
       </c>
-      <c r="K21" s="3">
-        <v>0</v>
-      </c>
-      <c r="L21" s="3">
-        <v>0</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N21" s="3" t="s">
-        <v>4</v>
+      <c r="M21" s="3">
+        <v>0</v>
+      </c>
+      <c r="N21" s="3">
+        <v>0</v>
       </c>
       <c r="O21" s="3" t="s">
         <v>4</v>
@@ -1818,39 +1891,39 @@
       <c r="Q21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R21" s="3">
-        <v>0</v>
+      <c r="R21" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U21" s="3">
-        <v>0</v>
-      </c>
-      <c r="V21" s="3">
+      <c r="T21" s="3">
+        <v>0</v>
+      </c>
+      <c r="U21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W21" s="3">
+        <v>0</v>
+      </c>
+      <c r="X21" s="3">
         <v>-200</v>
       </c>
-      <c r="W21" s="3">
-        <v>0</v>
-      </c>
-      <c r="X21" s="3">
-        <v>0</v>
-      </c>
       <c r="Y21" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z21" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA21" s="3">
         <v>-100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>-100</v>
       </c>
-      <c r="AA21" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB21" s="3">
-        <v>0</v>
-      </c>
       <c r="AC21" s="3">
         <v>0</v>
       </c>
@@ -1860,8 +1933,14 @@
       <c r="AE21" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF21" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG21" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1949,86 +2028,92 @@
       <c r="AE22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E23" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F23" s="3">
         <v>0</v>
       </c>
       <c r="G23" s="3">
+        <v>0</v>
+      </c>
+      <c r="H23" s="3">
+        <v>0</v>
+      </c>
+      <c r="I23" s="3">
         <v>100</v>
       </c>
-      <c r="H23" s="3">
-        <v>0</v>
-      </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
+        <v>0</v>
+      </c>
+      <c r="K23" s="3">
         <v>-100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-100</v>
       </c>
-      <c r="K23" s="3">
-        <v>0</v>
-      </c>
-      <c r="L23" s="3">
-        <v>0</v>
-      </c>
       <c r="M23" s="3">
+        <v>0</v>
+      </c>
+      <c r="N23" s="3">
+        <v>0</v>
+      </c>
+      <c r="O23" s="3">
         <v>-300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-100</v>
       </c>
-      <c r="P23" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q23" s="3">
-        <v>0</v>
-      </c>
       <c r="R23" s="3">
         <v>0</v>
       </c>
       <c r="S23" s="3">
+        <v>0</v>
+      </c>
+      <c r="T23" s="3">
+        <v>0</v>
+      </c>
+      <c r="U23" s="3">
         <v>-400</v>
       </c>
-      <c r="T23" s="3">
-        <v>0</v>
-      </c>
-      <c r="U23" s="3">
-        <v>0</v>
-      </c>
       <c r="V23" s="3">
+        <v>0</v>
+      </c>
+      <c r="W23" s="3">
+        <v>0</v>
+      </c>
+      <c r="X23" s="3">
         <v>-200</v>
       </c>
-      <c r="W23" s="3">
-        <v>0</v>
-      </c>
-      <c r="X23" s="3">
-        <v>0</v>
-      </c>
       <c r="Y23" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA23" s="3">
         <v>-100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-100</v>
       </c>
-      <c r="AA23" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB23" s="3">
-        <v>0</v>
-      </c>
       <c r="AC23" s="3">
         <v>0</v>
       </c>
@@ -2038,8 +2123,14 @@
       <c r="AE23" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2118,17 +2209,23 @@
       <c r="AB24" s="3">
         <v>0</v>
       </c>
-      <c r="AC24" s="3" t="s">
-        <v>4</v>
+      <c r="AC24" s="3">
+        <v>0</v>
       </c>
       <c r="AD24" s="3">
         <v>0</v>
       </c>
-      <c r="AE24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AE24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2216,86 +2313,92 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E26" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F26" s="3">
         <v>0</v>
       </c>
       <c r="G26" s="3">
+        <v>0</v>
+      </c>
+      <c r="H26" s="3">
+        <v>0</v>
+      </c>
+      <c r="I26" s="3">
         <v>100</v>
       </c>
-      <c r="H26" s="3">
-        <v>0</v>
-      </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
+        <v>0</v>
+      </c>
+      <c r="K26" s="3">
         <v>-100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-100</v>
       </c>
-      <c r="K26" s="3">
-        <v>0</v>
-      </c>
-      <c r="L26" s="3">
-        <v>0</v>
-      </c>
       <c r="M26" s="3">
+        <v>0</v>
+      </c>
+      <c r="N26" s="3">
+        <v>0</v>
+      </c>
+      <c r="O26" s="3">
         <v>-300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-100</v>
       </c>
-      <c r="P26" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="3">
-        <v>0</v>
-      </c>
       <c r="R26" s="3">
         <v>0</v>
       </c>
       <c r="S26" s="3">
+        <v>0</v>
+      </c>
+      <c r="T26" s="3">
+        <v>0</v>
+      </c>
+      <c r="U26" s="3">
         <v>-400</v>
       </c>
-      <c r="T26" s="3">
-        <v>0</v>
-      </c>
-      <c r="U26" s="3">
-        <v>0</v>
-      </c>
       <c r="V26" s="3">
+        <v>0</v>
+      </c>
+      <c r="W26" s="3">
+        <v>0</v>
+      </c>
+      <c r="X26" s="3">
         <v>-200</v>
       </c>
-      <c r="W26" s="3">
-        <v>0</v>
-      </c>
-      <c r="X26" s="3">
-        <v>0</v>
-      </c>
       <c r="Y26" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA26" s="3">
         <v>-100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-100</v>
       </c>
-      <c r="AA26" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB26" s="3">
-        <v>0</v>
-      </c>
       <c r="AC26" s="3">
         <v>0</v>
       </c>
@@ -2305,86 +2408,92 @@
       <c r="AE26" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E27" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F27" s="3">
         <v>0</v>
       </c>
       <c r="G27" s="3">
+        <v>0</v>
+      </c>
+      <c r="H27" s="3">
+        <v>0</v>
+      </c>
+      <c r="I27" s="3">
         <v>100</v>
       </c>
-      <c r="H27" s="3">
-        <v>0</v>
-      </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
+        <v>0</v>
+      </c>
+      <c r="K27" s="3">
         <v>-100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-100</v>
       </c>
-      <c r="K27" s="3">
-        <v>0</v>
-      </c>
-      <c r="L27" s="3">
-        <v>0</v>
-      </c>
       <c r="M27" s="3">
+        <v>0</v>
+      </c>
+      <c r="N27" s="3">
+        <v>0</v>
+      </c>
+      <c r="O27" s="3">
         <v>-300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-100</v>
       </c>
-      <c r="P27" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="3">
-        <v>0</v>
-      </c>
       <c r="R27" s="3">
         <v>0</v>
       </c>
       <c r="S27" s="3">
+        <v>0</v>
+      </c>
+      <c r="T27" s="3">
+        <v>0</v>
+      </c>
+      <c r="U27" s="3">
         <v>-400</v>
       </c>
-      <c r="T27" s="3">
-        <v>0</v>
-      </c>
-      <c r="U27" s="3">
-        <v>0</v>
-      </c>
       <c r="V27" s="3">
+        <v>0</v>
+      </c>
+      <c r="W27" s="3">
+        <v>0</v>
+      </c>
+      <c r="X27" s="3">
         <v>-200</v>
       </c>
-      <c r="W27" s="3">
-        <v>0</v>
-      </c>
-      <c r="X27" s="3">
-        <v>0</v>
-      </c>
       <c r="Y27" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA27" s="3">
         <v>-100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-100</v>
       </c>
-      <c r="AA27" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB27" s="3">
-        <v>0</v>
-      </c>
       <c r="AC27" s="3">
         <v>0</v>
       </c>
@@ -2394,8 +2503,14 @@
       <c r="AE27" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2483,8 +2598,14 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2572,8 +2693,14 @@
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2661,8 +2788,14 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2750,8 +2883,14 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2839,86 +2978,92 @@
       <c r="AE32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E33" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F33" s="3">
         <v>0</v>
       </c>
       <c r="G33" s="3">
+        <v>0</v>
+      </c>
+      <c r="H33" s="3">
+        <v>0</v>
+      </c>
+      <c r="I33" s="3">
         <v>100</v>
       </c>
-      <c r="H33" s="3">
-        <v>0</v>
-      </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
+        <v>0</v>
+      </c>
+      <c r="K33" s="3">
         <v>-100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-100</v>
       </c>
-      <c r="K33" s="3">
-        <v>0</v>
-      </c>
-      <c r="L33" s="3">
-        <v>0</v>
-      </c>
       <c r="M33" s="3">
+        <v>0</v>
+      </c>
+      <c r="N33" s="3">
+        <v>0</v>
+      </c>
+      <c r="O33" s="3">
         <v>-300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-100</v>
       </c>
-      <c r="P33" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q33" s="3">
-        <v>0</v>
-      </c>
       <c r="R33" s="3">
         <v>0</v>
       </c>
       <c r="S33" s="3">
+        <v>0</v>
+      </c>
+      <c r="T33" s="3">
+        <v>0</v>
+      </c>
+      <c r="U33" s="3">
         <v>-400</v>
       </c>
-      <c r="T33" s="3">
-        <v>0</v>
-      </c>
-      <c r="U33" s="3">
-        <v>0</v>
-      </c>
       <c r="V33" s="3">
+        <v>0</v>
+      </c>
+      <c r="W33" s="3">
+        <v>0</v>
+      </c>
+      <c r="X33" s="3">
         <v>-200</v>
       </c>
-      <c r="W33" s="3">
-        <v>0</v>
-      </c>
-      <c r="X33" s="3">
-        <v>0</v>
-      </c>
       <c r="Y33" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA33" s="3">
         <v>-100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-100</v>
       </c>
-      <c r="AA33" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB33" s="3">
-        <v>0</v>
-      </c>
       <c r="AC33" s="3">
         <v>0</v>
       </c>
@@ -2928,8 +3073,14 @@
       <c r="AE33" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3017,86 +3168,92 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E35" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F35" s="3">
         <v>0</v>
       </c>
       <c r="G35" s="3">
+        <v>0</v>
+      </c>
+      <c r="H35" s="3">
+        <v>0</v>
+      </c>
+      <c r="I35" s="3">
         <v>100</v>
       </c>
-      <c r="H35" s="3">
-        <v>0</v>
-      </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
+        <v>0</v>
+      </c>
+      <c r="K35" s="3">
         <v>-100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-100</v>
       </c>
-      <c r="K35" s="3">
-        <v>0</v>
-      </c>
-      <c r="L35" s="3">
-        <v>0</v>
-      </c>
       <c r="M35" s="3">
+        <v>0</v>
+      </c>
+      <c r="N35" s="3">
+        <v>0</v>
+      </c>
+      <c r="O35" s="3">
         <v>-300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-100</v>
       </c>
-      <c r="P35" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q35" s="3">
-        <v>0</v>
-      </c>
       <c r="R35" s="3">
         <v>0</v>
       </c>
       <c r="S35" s="3">
+        <v>0</v>
+      </c>
+      <c r="T35" s="3">
+        <v>0</v>
+      </c>
+      <c r="U35" s="3">
         <v>-400</v>
       </c>
-      <c r="T35" s="3">
-        <v>0</v>
-      </c>
-      <c r="U35" s="3">
-        <v>0</v>
-      </c>
       <c r="V35" s="3">
+        <v>0</v>
+      </c>
+      <c r="W35" s="3">
+        <v>0</v>
+      </c>
+      <c r="X35" s="3">
         <v>-200</v>
       </c>
-      <c r="W35" s="3">
-        <v>0</v>
-      </c>
-      <c r="X35" s="3">
-        <v>0</v>
-      </c>
       <c r="Y35" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA35" s="3">
         <v>-100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-100</v>
       </c>
-      <c r="AA35" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB35" s="3">
-        <v>0</v>
-      </c>
       <c r="AC35" s="3">
         <v>0</v>
       </c>
@@ -3106,102 +3263,114 @@
       <c r="AE35" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44135</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44043</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>43951</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43861</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43769</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43677</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43585</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43496</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43404</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43312</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43220</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43131</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43039</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>42947</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>42855</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42766</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42674</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42582</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3233,8 +3402,10 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3266,8 +3437,10 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -3275,25 +3448,25 @@
         <v>100</v>
       </c>
       <c r="E41" s="3">
+        <v>100</v>
+      </c>
+      <c r="F41" s="3">
+        <v>100</v>
+      </c>
+      <c r="G41" s="3">
         <v>200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>200</v>
       </c>
-      <c r="G41" s="3">
-        <v>0</v>
-      </c>
-      <c r="H41" s="3">
-        <v>0</v>
-      </c>
       <c r="I41" s="3">
         <v>0</v>
       </c>
       <c r="J41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L41" s="3">
         <v>100</v>
@@ -3302,17 +3475,17 @@
         <v>100</v>
       </c>
       <c r="N41" s="3">
+        <v>100</v>
+      </c>
+      <c r="O41" s="3">
+        <v>100</v>
+      </c>
+      <c r="P41" s="3">
         <v>200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>300</v>
       </c>
-      <c r="P41" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q41" s="3">
-        <v>0</v>
-      </c>
       <c r="R41" s="3">
         <v>0</v>
       </c>
@@ -3340,14 +3513,14 @@
       <c r="Z41" s="3">
         <v>0</v>
       </c>
-      <c r="AA41" s="3" t="s">
-        <v>4</v>
+      <c r="AA41" s="3">
+        <v>0</v>
       </c>
       <c r="AB41" s="3">
         <v>0</v>
       </c>
-      <c r="AC41" s="3">
-        <v>0</v>
+      <c r="AC41" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AD41" s="3">
         <v>0</v>
@@ -3355,8 +3528,14 @@
       <c r="AE41" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3444,8 +3623,14 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3533,8 +3718,14 @@
       <c r="AE43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3622,8 +3813,14 @@
       <c r="AE44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3633,11 +3830,11 @@
       <c r="E45" s="3">
         <v>0</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>4</v>
+      <c r="F45" s="3">
+        <v>0</v>
+      </c>
+      <c r="G45" s="3">
+        <v>0</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>4</v>
@@ -3648,11 +3845,11 @@
       <c r="J45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
-      </c>
-      <c r="L45" s="3">
-        <v>0</v>
+      <c r="K45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M45" s="3">
         <v>0</v>
@@ -3666,17 +3863,17 @@
       <c r="P45" s="3">
         <v>0</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S45" s="3">
-        <v>0</v>
-      </c>
-      <c r="T45" s="3">
-        <v>0</v>
+      <c r="Q45" s="3">
+        <v>0</v>
+      </c>
+      <c r="R45" s="3">
+        <v>0</v>
+      </c>
+      <c r="S45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U45" s="3">
         <v>0</v>
@@ -3693,14 +3890,14 @@
       <c r="Y45" s="3">
         <v>0</v>
       </c>
-      <c r="Z45" s="3" t="s">
-        <v>4</v>
+      <c r="Z45" s="3">
+        <v>0</v>
       </c>
       <c r="AA45" s="3">
         <v>0</v>
       </c>
-      <c r="AB45" s="3">
-        <v>0</v>
+      <c r="AB45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AC45" s="3">
         <v>0</v>
@@ -3711,8 +3908,14 @@
       <c r="AE45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3723,22 +3926,22 @@
         <v>200</v>
       </c>
       <c r="F46" s="3">
+        <v>100</v>
+      </c>
+      <c r="G46" s="3">
         <v>200</v>
       </c>
-      <c r="G46" s="3">
-        <v>0</v>
-      </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I46" s="3">
         <v>0</v>
       </c>
       <c r="J46" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K46" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L46" s="3">
         <v>100</v>
@@ -3747,17 +3950,17 @@
         <v>100</v>
       </c>
       <c r="N46" s="3">
+        <v>100</v>
+      </c>
+      <c r="O46" s="3">
+        <v>100</v>
+      </c>
+      <c r="P46" s="3">
         <v>200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>300</v>
       </c>
-      <c r="P46" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -3800,22 +4003,28 @@
       <c r="AE46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>4</v>
+      <c r="D47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F47" s="3">
+        <v>0</v>
+      </c>
+      <c r="G47" s="3">
+        <v>0</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>4</v>
@@ -3826,11 +4035,11 @@
       <c r="J47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -3889,8 +4098,14 @@
       <c r="AE47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3924,11 +4139,11 @@
       <c r="M48" s="3">
         <v>0</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O48" s="3" t="s">
-        <v>4</v>
+      <c r="N48" s="3">
+        <v>0</v>
+      </c>
+      <c r="O48" s="3">
+        <v>0</v>
       </c>
       <c r="P48" s="3" t="s">
         <v>4</v>
@@ -3939,11 +4154,11 @@
       <c r="R48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S48" s="3">
-        <v>0</v>
-      </c>
-      <c r="T48" s="3">
-        <v>0</v>
+      <c r="S48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U48" s="3">
         <v>0</v>
@@ -3978,8 +4193,14 @@
       <c r="AE48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF48" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4067,8 +4288,14 @@
       <c r="AE49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4156,8 +4383,14 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4245,8 +4478,14 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4334,8 +4573,14 @@
       <c r="AE52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4423,8 +4668,14 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
@@ -4435,22 +4686,22 @@
         <v>200</v>
       </c>
       <c r="F54" s="3">
+        <v>100</v>
+      </c>
+      <c r="G54" s="3">
         <v>200</v>
       </c>
-      <c r="G54" s="3">
-        <v>0</v>
-      </c>
       <c r="H54" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I54" s="3">
         <v>0</v>
       </c>
       <c r="J54" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K54" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L54" s="3">
         <v>100</v>
@@ -4459,17 +4710,17 @@
         <v>100</v>
       </c>
       <c r="N54" s="3">
+        <v>100</v>
+      </c>
+      <c r="O54" s="3">
+        <v>100</v>
+      </c>
+      <c r="P54" s="3">
         <v>200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>300</v>
       </c>
-      <c r="P54" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q54" s="3">
-        <v>0</v>
-      </c>
       <c r="R54" s="3">
         <v>0</v>
       </c>
@@ -4512,8 +4763,14 @@
       <c r="AE54" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF54" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG54" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4545,8 +4802,10 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4578,16 +4837,18 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E57" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F57" s="3">
         <v>200</v>
@@ -4596,28 +4857,28 @@
         <v>200</v>
       </c>
       <c r="H57" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="I57" s="3">
         <v>200</v>
       </c>
       <c r="J57" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="K57" s="3">
         <v>200</v>
       </c>
       <c r="L57" s="3">
+        <v>200</v>
+      </c>
+      <c r="M57" s="3">
+        <v>200</v>
+      </c>
+      <c r="N57" s="3">
         <v>100</v>
       </c>
-      <c r="M57" s="3">
-        <v>0</v>
-      </c>
-      <c r="N57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O57" s="3" t="s">
-        <v>4</v>
+      <c r="O57" s="3">
+        <v>0</v>
       </c>
       <c r="P57" s="3" t="s">
         <v>4</v>
@@ -4628,11 +4889,11 @@
       <c r="R57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S57" s="3">
-        <v>0</v>
-      </c>
-      <c r="T57" s="3">
-        <v>0</v>
+      <c r="S57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T57" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U57" s="3">
         <v>0</v>
@@ -4655,20 +4916,26 @@
       <c r="AA57" s="3">
         <v>0</v>
       </c>
-      <c r="AB57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD57" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE57" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AB57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4756,8 +5023,14 @@
       <c r="AE58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4786,50 +5059,50 @@
         <v>600</v>
       </c>
       <c r="L59" s="3">
+        <v>600</v>
+      </c>
+      <c r="M59" s="3">
+        <v>600</v>
+      </c>
+      <c r="N59" s="3">
         <v>700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>200</v>
-      </c>
-      <c r="Q59" s="3">
-        <v>100</v>
-      </c>
-      <c r="R59" s="3">
-        <v>100</v>
       </c>
       <c r="S59" s="3">
         <v>100</v>
       </c>
       <c r="T59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U59" s="3">
+        <v>100</v>
+      </c>
+      <c r="V59" s="3">
+        <v>0</v>
+      </c>
+      <c r="W59" s="3">
         <v>300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>100</v>
       </c>
-      <c r="Y59" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z59" s="3">
-        <v>0</v>
-      </c>
       <c r="AA59" s="3">
         <v>0</v>
       </c>
@@ -4845,16 +5118,22 @@
       <c r="AE59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="E60" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="F60" s="3">
         <v>800</v>
@@ -4872,7 +5151,7 @@
         <v>800</v>
       </c>
       <c r="K60" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="L60" s="3">
         <v>800</v>
@@ -4881,37 +5160,37 @@
         <v>700</v>
       </c>
       <c r="N60" s="3">
+        <v>800</v>
+      </c>
+      <c r="O60" s="3">
+        <v>700</v>
+      </c>
+      <c r="P60" s="3">
         <v>500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>200</v>
-      </c>
-      <c r="Q60" s="3">
-        <v>100</v>
-      </c>
-      <c r="R60" s="3">
-        <v>100</v>
       </c>
       <c r="S60" s="3">
         <v>100</v>
       </c>
       <c r="T60" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U60" s="3">
+        <v>100</v>
+      </c>
+      <c r="V60" s="3">
+        <v>0</v>
+      </c>
+      <c r="W60" s="3">
         <v>300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>300</v>
-      </c>
-      <c r="W60" s="3">
-        <v>100</v>
-      </c>
-      <c r="X60" s="3">
-        <v>100</v>
       </c>
       <c r="Y60" s="3">
         <v>100</v>
@@ -4920,10 +5199,10 @@
         <v>100</v>
       </c>
       <c r="AA60" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB60" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC60" s="3">
         <v>0</v>
@@ -4934,8 +5213,14 @@
       <c r="AE60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5023,8 +5308,14 @@
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5112,8 +5403,14 @@
       <c r="AE62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5201,8 +5498,14 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5290,8 +5593,14 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5379,16 +5688,22 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="E66" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="F66" s="3">
         <v>800</v>
@@ -5406,7 +5721,7 @@
         <v>800</v>
       </c>
       <c r="K66" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="L66" s="3">
         <v>800</v>
@@ -5415,37 +5730,37 @@
         <v>700</v>
       </c>
       <c r="N66" s="3">
+        <v>800</v>
+      </c>
+      <c r="O66" s="3">
+        <v>700</v>
+      </c>
+      <c r="P66" s="3">
         <v>500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>200</v>
-      </c>
-      <c r="Q66" s="3">
-        <v>100</v>
-      </c>
-      <c r="R66" s="3">
-        <v>100</v>
       </c>
       <c r="S66" s="3">
         <v>100</v>
       </c>
       <c r="T66" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U66" s="3">
+        <v>100</v>
+      </c>
+      <c r="V66" s="3">
+        <v>0</v>
+      </c>
+      <c r="W66" s="3">
         <v>300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>300</v>
-      </c>
-      <c r="W66" s="3">
-        <v>100</v>
-      </c>
-      <c r="X66" s="3">
-        <v>100</v>
       </c>
       <c r="Y66" s="3">
         <v>100</v>
@@ -5454,10 +5769,10 @@
         <v>100</v>
       </c>
       <c r="AA66" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB66" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC66" s="3">
         <v>0</v>
@@ -5468,8 +5783,14 @@
       <c r="AE66" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF66" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG66" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5501,8 +5822,10 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5590,8 +5913,14 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5679,8 +6008,14 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5768,8 +6103,14 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5857,73 +6198,79 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="F72" s="3">
         <v>-1300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-1300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-1200</v>
-      </c>
-      <c r="G72" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="H72" s="3">
-        <v>-1300</v>
       </c>
       <c r="I72" s="3">
         <v>-1200</v>
       </c>
       <c r="J72" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="K72" s="3">
         <v>-1200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="M72" s="3">
         <v>-1100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-1100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-1000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-400</v>
-      </c>
-      <c r="W72" s="3">
-        <v>-100</v>
-      </c>
-      <c r="X72" s="3">
-        <v>-100</v>
       </c>
       <c r="Y72" s="3">
         <v>-100</v>
@@ -5932,10 +6279,10 @@
         <v>-100</v>
       </c>
       <c r="AA72" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AB72" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AC72" s="3">
         <v>0</v>
@@ -5946,8 +6293,14 @@
       <c r="AE72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF72" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6035,8 +6388,14 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6124,8 +6483,14 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6213,73 +6578,79 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E76" s="3">
+        <v>-500</v>
+      </c>
+      <c r="F76" s="3">
         <v>-700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>-600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>-600</v>
-      </c>
-      <c r="G76" s="3">
-        <v>-800</v>
-      </c>
-      <c r="H76" s="3">
-        <v>-800</v>
       </c>
       <c r="I76" s="3">
         <v>-800</v>
       </c>
       <c r="J76" s="3">
-        <v>-700</v>
+        <v>-800</v>
       </c>
       <c r="K76" s="3">
-        <v>-700</v>
+        <v>-800</v>
       </c>
       <c r="L76" s="3">
         <v>-700</v>
       </c>
       <c r="M76" s="3">
+        <v>-700</v>
+      </c>
+      <c r="N76" s="3">
+        <v>-700</v>
+      </c>
+      <c r="O76" s="3">
         <v>-600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>-300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>-200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>-200</v>
-      </c>
-      <c r="Q76" s="3">
-        <v>-100</v>
-      </c>
-      <c r="R76" s="3">
-        <v>-100</v>
       </c>
       <c r="S76" s="3">
         <v>-100</v>
       </c>
       <c r="T76" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="U76" s="3">
+        <v>-100</v>
+      </c>
+      <c r="V76" s="3">
+        <v>0</v>
+      </c>
+      <c r="W76" s="3">
         <v>-300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>-300</v>
-      </c>
-      <c r="W76" s="3">
-        <v>-100</v>
-      </c>
-      <c r="X76" s="3">
-        <v>-100</v>
       </c>
       <c r="Y76" s="3">
         <v>-100</v>
@@ -6288,10 +6659,10 @@
         <v>-100</v>
       </c>
       <c r="AA76" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AB76" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AC76" s="3">
         <v>0</v>
@@ -6302,8 +6673,14 @@
       <c r="AE76" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF76" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG76" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6391,180 +6768,192 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44135</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44043</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>43951</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43861</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43769</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43677</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43585</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43496</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43404</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43312</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43220</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43131</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43039</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>42947</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>42855</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42766</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42674</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42582</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E81" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F81" s="3">
         <v>0</v>
       </c>
       <c r="G81" s="3">
+        <v>0</v>
+      </c>
+      <c r="H81" s="3">
+        <v>0</v>
+      </c>
+      <c r="I81" s="3">
         <v>100</v>
       </c>
-      <c r="H81" s="3">
-        <v>0</v>
-      </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
+        <v>0</v>
+      </c>
+      <c r="K81" s="3">
         <v>-100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-100</v>
       </c>
-      <c r="K81" s="3">
-        <v>0</v>
-      </c>
-      <c r="L81" s="3">
-        <v>0</v>
-      </c>
       <c r="M81" s="3">
+        <v>0</v>
+      </c>
+      <c r="N81" s="3">
+        <v>0</v>
+      </c>
+      <c r="O81" s="3">
         <v>-300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-100</v>
       </c>
-      <c r="P81" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q81" s="3">
-        <v>0</v>
-      </c>
       <c r="R81" s="3">
         <v>0</v>
       </c>
       <c r="S81" s="3">
+        <v>0</v>
+      </c>
+      <c r="T81" s="3">
+        <v>0</v>
+      </c>
+      <c r="U81" s="3">
         <v>-400</v>
       </c>
-      <c r="T81" s="3">
-        <v>0</v>
-      </c>
-      <c r="U81" s="3">
-        <v>0</v>
-      </c>
       <c r="V81" s="3">
+        <v>0</v>
+      </c>
+      <c r="W81" s="3">
+        <v>0</v>
+      </c>
+      <c r="X81" s="3">
         <v>-200</v>
       </c>
-      <c r="W81" s="3">
-        <v>0</v>
-      </c>
-      <c r="X81" s="3">
-        <v>0</v>
-      </c>
       <c r="Y81" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA81" s="3">
         <v>-100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-100</v>
       </c>
-      <c r="AA81" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB81" s="3">
-        <v>0</v>
-      </c>
       <c r="AC81" s="3">
         <v>0</v>
       </c>
@@ -6574,8 +6963,14 @@
       <c r="AE81" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6607,13 +7002,15 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>0</v>
+      <c r="D83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E83" s="3">
         <v>0</v>
@@ -6639,11 +7036,11 @@
       <c r="L83" s="3">
         <v>0</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N83" s="3" t="s">
-        <v>4</v>
+      <c r="M83" s="3">
+        <v>0</v>
+      </c>
+      <c r="N83" s="3">
+        <v>0</v>
       </c>
       <c r="O83" s="3" t="s">
         <v>4</v>
@@ -6654,11 +7051,11 @@
       <c r="Q83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R83" s="3">
-        <v>0</v>
-      </c>
-      <c r="S83" s="3">
-        <v>0</v>
+      <c r="R83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T83" s="3">
         <v>0</v>
@@ -6696,8 +7093,14 @@
       <c r="AE83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6785,8 +7188,14 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6874,8 +7283,14 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6963,8 +7378,14 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7052,8 +7473,14 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7141,8 +7568,14 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -7150,14 +7583,14 @@
         <v>0</v>
       </c>
       <c r="E89" s="3">
+        <v>0</v>
+      </c>
+      <c r="F89" s="3">
+        <v>0</v>
+      </c>
+      <c r="G89" s="3">
         <v>-100</v>
       </c>
-      <c r="F89" s="3">
-        <v>0</v>
-      </c>
-      <c r="G89" s="3">
-        <v>0</v>
-      </c>
       <c r="H89" s="3">
         <v>0</v>
       </c>
@@ -7174,13 +7607,13 @@
         <v>0</v>
       </c>
       <c r="M89" s="3">
+        <v>0</v>
+      </c>
+      <c r="N89" s="3">
+        <v>0</v>
+      </c>
+      <c r="O89" s="3">
         <v>-300</v>
-      </c>
-      <c r="N89" s="3">
-        <v>-100</v>
-      </c>
-      <c r="O89" s="3">
-        <v>0</v>
       </c>
       <c r="P89" s="3">
         <v>-100</v>
@@ -7189,32 +7622,32 @@
         <v>0</v>
       </c>
       <c r="R89" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="S89" s="3">
         <v>0</v>
       </c>
       <c r="T89" s="3">
+        <v>0</v>
+      </c>
+      <c r="U89" s="3">
+        <v>0</v>
+      </c>
+      <c r="V89" s="3">
         <v>300</v>
       </c>
-      <c r="U89" s="3">
-        <v>0</v>
-      </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
+        <v>0</v>
+      </c>
+      <c r="X89" s="3">
         <v>-200</v>
       </c>
-      <c r="W89" s="3">
-        <v>0</v>
-      </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z89" s="3">
         <v>-100</v>
       </c>
-      <c r="Y89" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z89" s="3">
-        <v>0</v>
-      </c>
       <c r="AA89" s="3">
         <v>0</v>
       </c>
@@ -7230,8 +7663,14 @@
       <c r="AE89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7263,8 +7702,10 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7352,8 +7793,14 @@
       <c r="AE91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7441,8 +7888,14 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7530,37 +7983,43 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>0</v>
+      <c r="D94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
-      <c r="L94" s="3">
-        <v>0</v>
+      <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M94" s="3">
         <v>0</v>
@@ -7619,8 +8078,14 @@
       <c r="AE94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7652,8 +8117,10 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7741,8 +8208,14 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7830,8 +8303,14 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7919,8 +8398,14 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8008,8 +8493,14 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8020,44 +8511,44 @@
         <v>0</v>
       </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>200</v>
       </c>
-      <c r="G100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I100" s="3" t="s">
         <v>4</v>
       </c>
       <c r="J100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
-      <c r="L100" s="3">
-        <v>0</v>
+      <c r="K100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>200</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>100</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
       <c r="S100" s="3">
         <v>0</v>
       </c>
@@ -8068,20 +8559,20 @@
         <v>0</v>
       </c>
       <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3">
         <v>200</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3">
         <v>100</v>
       </c>
-      <c r="Y100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z100" s="3">
-        <v>0</v>
-      </c>
       <c r="AA100" s="3">
         <v>0</v>
       </c>
@@ -8097,8 +8588,14 @@
       <c r="AE100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8186,8 +8683,14 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -8195,17 +8698,17 @@
         <v>0</v>
       </c>
       <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
         <v>-100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>200</v>
       </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
       <c r="I102" s="3">
         <v>0</v>
       </c>
@@ -8219,20 +8722,20 @@
         <v>0</v>
       </c>
       <c r="M102" s="3">
+        <v>0</v>
+      </c>
+      <c r="N102" s="3">
+        <v>0</v>
+      </c>
+      <c r="O102" s="3">
         <v>-100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>300</v>
       </c>
-      <c r="P102" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q102" s="3">
-        <v>0</v>
-      </c>
       <c r="R102" s="3">
         <v>0</v>
       </c>
@@ -8273,6 +8776,12 @@
         <v>0</v>
       </c>
       <c r="AE102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SNTW_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SNTW_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="92">
   <si>
     <t>SNTW</t>
   </si>
@@ -656,144 +656,148 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44135</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44043</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43951</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43861</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43769</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43677</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43585</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43496</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43404</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43312</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43220</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43131</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43039</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42947</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42855</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42766</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42674</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42582</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -887,8 +891,11 @@
       <c r="AG8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -970,8 +977,8 @@
       <c r="AC9" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AD9" s="3">
-        <v>0</v>
+      <c r="AD9" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AE9" s="3">
         <v>0</v>
@@ -982,8 +989,11 @@
       <c r="AG9" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH9" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1065,8 +1075,8 @@
       <c r="AC10" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AD10" s="3">
-        <v>0</v>
+      <c r="AD10" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AE10" s="3">
         <v>0</v>
@@ -1077,8 +1087,11 @@
       <c r="AG10" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH10" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1112,8 +1125,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1207,8 +1221,11 @@
       <c r="AG12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1302,31 +1319,34 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="3">
         <v>-200</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>4</v>
+      <c r="I14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>4</v>
@@ -1334,39 +1354,39 @@
       <c r="L14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N14" s="3">
         <v>-100</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>4</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>4</v>
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R14" s="3">
+        <v>0</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="T14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>300</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>-300</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1376,8 +1396,8 @@
       <c r="Z14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
+      <c r="AA14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB14" s="3">
         <v>0</v>
@@ -1397,8 +1417,11 @@
       <c r="AG14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1492,8 +1515,11 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1524,8 +1550,9 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1533,46 +1560,46 @@
         <v>100</v>
       </c>
       <c r="E17" s="3">
+        <v>100</v>
+      </c>
+      <c r="F17" s="3">
         <v>-100</v>
       </c>
-      <c r="F17" s="3">
-        <v>0</v>
-      </c>
       <c r="G17" s="3">
+        <v>0</v>
+      </c>
+      <c r="H17" s="3">
         <v>100</v>
       </c>
-      <c r="H17" s="3">
-        <v>0</v>
-      </c>
       <c r="I17" s="3">
+        <v>0</v>
+      </c>
+      <c r="J17" s="3">
         <v>-100</v>
       </c>
-      <c r="J17" s="3">
-        <v>0</v>
-      </c>
       <c r="K17" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L17" s="3">
         <v>100</v>
       </c>
       <c r="M17" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N17" s="3">
         <v>0</v>
       </c>
       <c r="O17" s="3">
+        <v>0</v>
+      </c>
+      <c r="P17" s="3">
         <v>300</v>
-      </c>
-      <c r="P17" s="3">
-        <v>100</v>
       </c>
       <c r="Q17" s="3">
         <v>100</v>
       </c>
       <c r="R17" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S17" s="3">
         <v>0</v>
@@ -1581,31 +1608,31 @@
         <v>0</v>
       </c>
       <c r="U17" s="3">
+        <v>0</v>
+      </c>
+      <c r="V17" s="3">
         <v>400</v>
       </c>
-      <c r="V17" s="3">
-        <v>0</v>
-      </c>
       <c r="W17" s="3">
         <v>0</v>
       </c>
       <c r="X17" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="3">
         <v>200</v>
       </c>
-      <c r="Y17" s="3">
-        <v>0</v>
-      </c>
       <c r="Z17" s="3">
         <v>0</v>
       </c>
       <c r="AA17" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB17" s="3">
         <v>100</v>
       </c>
       <c r="AC17" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AD17" s="3">
         <v>0</v>
@@ -1619,8 +1646,11 @@
       <c r="AG17" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1628,46 +1658,46 @@
         <v>4</v>
       </c>
       <c r="E18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F18" s="3">
         <v>100</v>
       </c>
-      <c r="F18" s="3">
-        <v>0</v>
-      </c>
       <c r="G18" s="3">
+        <v>0</v>
+      </c>
+      <c r="H18" s="3">
         <v>-100</v>
       </c>
-      <c r="H18" s="3">
-        <v>0</v>
-      </c>
       <c r="I18" s="3">
+        <v>0</v>
+      </c>
+      <c r="J18" s="3">
         <v>100</v>
       </c>
-      <c r="J18" s="3">
-        <v>0</v>
-      </c>
       <c r="K18" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L18" s="3">
         <v>-100</v>
       </c>
       <c r="M18" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="N18" s="3">
         <v>0</v>
       </c>
       <c r="O18" s="3">
+        <v>0</v>
+      </c>
+      <c r="P18" s="3">
         <v>-300</v>
-      </c>
-      <c r="P18" s="3">
-        <v>-100</v>
       </c>
       <c r="Q18" s="3">
         <v>-100</v>
       </c>
       <c r="R18" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="S18" s="3">
         <v>0</v>
@@ -1676,31 +1706,31 @@
         <v>0</v>
       </c>
       <c r="U18" s="3">
+        <v>0</v>
+      </c>
+      <c r="V18" s="3">
         <v>-400</v>
       </c>
-      <c r="V18" s="3">
-        <v>0</v>
-      </c>
       <c r="W18" s="3">
         <v>0</v>
       </c>
       <c r="X18" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="3">
         <v>-200</v>
       </c>
-      <c r="Y18" s="3">
-        <v>0</v>
-      </c>
       <c r="Z18" s="3">
         <v>0</v>
       </c>
       <c r="AA18" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AB18" s="3">
         <v>-100</v>
       </c>
       <c r="AC18" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AD18" s="3">
         <v>0</v>
@@ -1714,8 +1744,11 @@
       <c r="AG18" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1749,8 +1782,9 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1844,8 +1878,11 @@
       <c r="AG20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1853,11 +1890,11 @@
         <v>4</v>
       </c>
       <c r="E21" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F21" s="3">
         <v>100</v>
       </c>
-      <c r="F21" s="3">
-        <v>0</v>
-      </c>
       <c r="G21" s="3">
         <v>0</v>
       </c>
@@ -1865,25 +1902,25 @@
         <v>0</v>
       </c>
       <c r="I21" s="3">
+        <v>0</v>
+      </c>
+      <c r="J21" s="3">
         <v>100</v>
       </c>
-      <c r="J21" s="3">
-        <v>0</v>
-      </c>
       <c r="K21" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L21" s="3">
         <v>-100</v>
       </c>
       <c r="M21" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="N21" s="3">
         <v>0</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>4</v>
+      <c r="O21" s="3">
+        <v>0</v>
       </c>
       <c r="P21" s="3" t="s">
         <v>4</v>
@@ -1897,35 +1934,35 @@
       <c r="S21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T21" s="3">
-        <v>0</v>
-      </c>
-      <c r="U21" s="3" t="s">
-        <v>4</v>
+      <c r="T21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U21" s="3">
+        <v>0</v>
       </c>
       <c r="V21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W21" s="3">
-        <v>0</v>
+      <c r="W21" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X21" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y21" s="3">
         <v>-200</v>
       </c>
-      <c r="Y21" s="3">
-        <v>0</v>
-      </c>
       <c r="Z21" s="3">
         <v>0</v>
       </c>
       <c r="AA21" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AB21" s="3">
         <v>-100</v>
       </c>
       <c r="AC21" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AD21" s="3">
         <v>0</v>
@@ -1939,8 +1976,11 @@
       <c r="AG21" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH21" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2034,8 +2074,11 @@
       <c r="AG22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2043,11 +2086,11 @@
         <v>-100</v>
       </c>
       <c r="E23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F23" s="3">
         <v>100</v>
       </c>
-      <c r="F23" s="3">
-        <v>0</v>
-      </c>
       <c r="G23" s="3">
         <v>0</v>
       </c>
@@ -2055,34 +2098,34 @@
         <v>0</v>
       </c>
       <c r="I23" s="3">
+        <v>0</v>
+      </c>
+      <c r="J23" s="3">
         <v>100</v>
       </c>
-      <c r="J23" s="3">
-        <v>0</v>
-      </c>
       <c r="K23" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L23" s="3">
         <v>-100</v>
       </c>
       <c r="M23" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="N23" s="3">
         <v>0</v>
       </c>
       <c r="O23" s="3">
+        <v>0</v>
+      </c>
+      <c r="P23" s="3">
         <v>-300</v>
-      </c>
-      <c r="P23" s="3">
-        <v>-100</v>
       </c>
       <c r="Q23" s="3">
         <v>-100</v>
       </c>
       <c r="R23" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="S23" s="3">
         <v>0</v>
@@ -2091,31 +2134,31 @@
         <v>0</v>
       </c>
       <c r="U23" s="3">
+        <v>0</v>
+      </c>
+      <c r="V23" s="3">
         <v>-400</v>
       </c>
-      <c r="V23" s="3">
-        <v>0</v>
-      </c>
       <c r="W23" s="3">
         <v>0</v>
       </c>
       <c r="X23" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y23" s="3">
         <v>-200</v>
       </c>
-      <c r="Y23" s="3">
-        <v>0</v>
-      </c>
       <c r="Z23" s="3">
         <v>0</v>
       </c>
       <c r="AA23" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AB23" s="3">
         <v>-100</v>
       </c>
       <c r="AC23" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AD23" s="3">
         <v>0</v>
@@ -2129,8 +2172,11 @@
       <c r="AG23" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2215,17 +2261,20 @@
       <c r="AD24" s="3">
         <v>0</v>
       </c>
-      <c r="AE24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF24" s="3">
-        <v>0</v>
+      <c r="AE24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AG24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2319,8 +2368,11 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2328,11 +2380,11 @@
         <v>-100</v>
       </c>
       <c r="E26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F26" s="3">
         <v>100</v>
       </c>
-      <c r="F26" s="3">
-        <v>0</v>
-      </c>
       <c r="G26" s="3">
         <v>0</v>
       </c>
@@ -2340,34 +2392,34 @@
         <v>0</v>
       </c>
       <c r="I26" s="3">
+        <v>0</v>
+      </c>
+      <c r="J26" s="3">
         <v>100</v>
       </c>
-      <c r="J26" s="3">
-        <v>0</v>
-      </c>
       <c r="K26" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L26" s="3">
         <v>-100</v>
       </c>
       <c r="M26" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="N26" s="3">
         <v>0</v>
       </c>
       <c r="O26" s="3">
+        <v>0</v>
+      </c>
+      <c r="P26" s="3">
         <v>-300</v>
-      </c>
-      <c r="P26" s="3">
-        <v>-100</v>
       </c>
       <c r="Q26" s="3">
         <v>-100</v>
       </c>
       <c r="R26" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="S26" s="3">
         <v>0</v>
@@ -2376,31 +2428,31 @@
         <v>0</v>
       </c>
       <c r="U26" s="3">
+        <v>0</v>
+      </c>
+      <c r="V26" s="3">
         <v>-400</v>
       </c>
-      <c r="V26" s="3">
-        <v>0</v>
-      </c>
       <c r="W26" s="3">
         <v>0</v>
       </c>
       <c r="X26" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y26" s="3">
         <v>-200</v>
       </c>
-      <c r="Y26" s="3">
-        <v>0</v>
-      </c>
       <c r="Z26" s="3">
         <v>0</v>
       </c>
       <c r="AA26" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AB26" s="3">
         <v>-100</v>
       </c>
       <c r="AC26" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AD26" s="3">
         <v>0</v>
@@ -2414,8 +2466,11 @@
       <c r="AG26" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2423,11 +2478,11 @@
         <v>-100</v>
       </c>
       <c r="E27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F27" s="3">
         <v>100</v>
       </c>
-      <c r="F27" s="3">
-        <v>0</v>
-      </c>
       <c r="G27" s="3">
         <v>0</v>
       </c>
@@ -2435,34 +2490,34 @@
         <v>0</v>
       </c>
       <c r="I27" s="3">
+        <v>0</v>
+      </c>
+      <c r="J27" s="3">
         <v>100</v>
       </c>
-      <c r="J27" s="3">
-        <v>0</v>
-      </c>
       <c r="K27" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L27" s="3">
         <v>-100</v>
       </c>
       <c r="M27" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="N27" s="3">
         <v>0</v>
       </c>
       <c r="O27" s="3">
+        <v>0</v>
+      </c>
+      <c r="P27" s="3">
         <v>-300</v>
-      </c>
-      <c r="P27" s="3">
-        <v>-100</v>
       </c>
       <c r="Q27" s="3">
         <v>-100</v>
       </c>
       <c r="R27" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="S27" s="3">
         <v>0</v>
@@ -2471,31 +2526,31 @@
         <v>0</v>
       </c>
       <c r="U27" s="3">
+        <v>0</v>
+      </c>
+      <c r="V27" s="3">
         <v>-400</v>
       </c>
-      <c r="V27" s="3">
-        <v>0</v>
-      </c>
       <c r="W27" s="3">
         <v>0</v>
       </c>
       <c r="X27" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y27" s="3">
         <v>-200</v>
       </c>
-      <c r="Y27" s="3">
-        <v>0</v>
-      </c>
       <c r="Z27" s="3">
         <v>0</v>
       </c>
       <c r="AA27" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AB27" s="3">
         <v>-100</v>
       </c>
       <c r="AC27" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AD27" s="3">
         <v>0</v>
@@ -2509,8 +2564,11 @@
       <c r="AG27" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2604,8 +2662,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2699,8 +2760,11 @@
       <c r="AG29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2794,8 +2858,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2889,8 +2956,11 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2984,8 +3054,11 @@
       <c r="AG32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2993,11 +3066,11 @@
         <v>-100</v>
       </c>
       <c r="E33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F33" s="3">
         <v>100</v>
       </c>
-      <c r="F33" s="3">
-        <v>0</v>
-      </c>
       <c r="G33" s="3">
         <v>0</v>
       </c>
@@ -3005,34 +3078,34 @@
         <v>0</v>
       </c>
       <c r="I33" s="3">
+        <v>0</v>
+      </c>
+      <c r="J33" s="3">
         <v>100</v>
       </c>
-      <c r="J33" s="3">
-        <v>0</v>
-      </c>
       <c r="K33" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L33" s="3">
         <v>-100</v>
       </c>
       <c r="M33" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="N33" s="3">
         <v>0</v>
       </c>
       <c r="O33" s="3">
+        <v>0</v>
+      </c>
+      <c r="P33" s="3">
         <v>-300</v>
-      </c>
-      <c r="P33" s="3">
-        <v>-100</v>
       </c>
       <c r="Q33" s="3">
         <v>-100</v>
       </c>
       <c r="R33" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="S33" s="3">
         <v>0</v>
@@ -3041,31 +3114,31 @@
         <v>0</v>
       </c>
       <c r="U33" s="3">
+        <v>0</v>
+      </c>
+      <c r="V33" s="3">
         <v>-400</v>
       </c>
-      <c r="V33" s="3">
-        <v>0</v>
-      </c>
       <c r="W33" s="3">
         <v>0</v>
       </c>
       <c r="X33" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y33" s="3">
         <v>-200</v>
       </c>
-      <c r="Y33" s="3">
-        <v>0</v>
-      </c>
       <c r="Z33" s="3">
         <v>0</v>
       </c>
       <c r="AA33" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AB33" s="3">
         <v>-100</v>
       </c>
       <c r="AC33" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AD33" s="3">
         <v>0</v>
@@ -3079,8 +3152,11 @@
       <c r="AG33" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3174,8 +3250,11 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3183,11 +3262,11 @@
         <v>-100</v>
       </c>
       <c r="E35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F35" s="3">
         <v>100</v>
       </c>
-      <c r="F35" s="3">
-        <v>0</v>
-      </c>
       <c r="G35" s="3">
         <v>0</v>
       </c>
@@ -3195,34 +3274,34 @@
         <v>0</v>
       </c>
       <c r="I35" s="3">
+        <v>0</v>
+      </c>
+      <c r="J35" s="3">
         <v>100</v>
       </c>
-      <c r="J35" s="3">
-        <v>0</v>
-      </c>
       <c r="K35" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L35" s="3">
         <v>-100</v>
       </c>
       <c r="M35" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="N35" s="3">
         <v>0</v>
       </c>
       <c r="O35" s="3">
+        <v>0</v>
+      </c>
+      <c r="P35" s="3">
         <v>-300</v>
-      </c>
-      <c r="P35" s="3">
-        <v>-100</v>
       </c>
       <c r="Q35" s="3">
         <v>-100</v>
       </c>
       <c r="R35" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="S35" s="3">
         <v>0</v>
@@ -3231,31 +3310,31 @@
         <v>0</v>
       </c>
       <c r="U35" s="3">
+        <v>0</v>
+      </c>
+      <c r="V35" s="3">
         <v>-400</v>
       </c>
-      <c r="V35" s="3">
-        <v>0</v>
-      </c>
       <c r="W35" s="3">
         <v>0</v>
       </c>
       <c r="X35" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y35" s="3">
         <v>-200</v>
       </c>
-      <c r="Y35" s="3">
-        <v>0</v>
-      </c>
       <c r="Z35" s="3">
         <v>0</v>
       </c>
       <c r="AA35" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AB35" s="3">
         <v>-100</v>
       </c>
       <c r="AC35" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AD35" s="3">
         <v>0</v>
@@ -3269,108 +3348,114 @@
       <c r="AG35" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44135</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44043</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43951</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43861</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43769</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43677</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43585</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43496</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43404</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43312</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43220</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43131</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43039</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42947</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42855</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42766</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42674</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42582</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3404,8 +3489,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3439,13 +3525,14 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E41" s="3">
         <v>100</v>
@@ -3454,13 +3541,13 @@
         <v>100</v>
       </c>
       <c r="G41" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H41" s="3">
         <v>200</v>
       </c>
       <c r="I41" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="J41" s="3">
         <v>0</v>
@@ -3469,7 +3556,7 @@
         <v>0</v>
       </c>
       <c r="L41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M41" s="3">
         <v>100</v>
@@ -3481,14 +3568,14 @@
         <v>100</v>
       </c>
       <c r="P41" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q41" s="3">
         <v>200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>300</v>
       </c>
-      <c r="R41" s="3">
-        <v>0</v>
-      </c>
       <c r="S41" s="3">
         <v>0</v>
       </c>
@@ -3519,11 +3606,11 @@
       <c r="AB41" s="3">
         <v>0</v>
       </c>
-      <c r="AC41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD41" s="3">
-        <v>0</v>
+      <c r="AC41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD41" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AE41" s="3">
         <v>0</v>
@@ -3534,8 +3621,11 @@
       <c r="AG41" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3629,8 +3719,11 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3724,8 +3817,11 @@
       <c r="AG43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3819,8 +3915,11 @@
       <c r="AG44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3836,8 +3935,8 @@
       <c r="G45" s="3">
         <v>0</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>4</v>
+      <c r="H45" s="3">
+        <v>0</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>4</v>
@@ -3851,8 +3950,8 @@
       <c r="L45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M45" s="3">
-        <v>0</v>
+      <c r="M45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N45" s="3">
         <v>0</v>
@@ -3869,14 +3968,14 @@
       <c r="R45" s="3">
         <v>0</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>4</v>
+      <c r="S45" s="3">
+        <v>0</v>
       </c>
       <c r="T45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U45" s="3">
-        <v>0</v>
+      <c r="U45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V45" s="3">
         <v>0</v>
@@ -3896,11 +3995,11 @@
       <c r="AA45" s="3">
         <v>0</v>
       </c>
-      <c r="AB45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC45" s="3">
-        <v>0</v>
+      <c r="AB45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AD45" s="3">
         <v>0</v>
@@ -3914,28 +4013,31 @@
       <c r="AG45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>200</v>
+      </c>
+      <c r="E46" s="3">
         <v>100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>100</v>
-      </c>
-      <c r="G46" s="3">
-        <v>200</v>
       </c>
       <c r="H46" s="3">
         <v>200</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="J46" s="3">
         <v>0</v>
@@ -3944,7 +4046,7 @@
         <v>0</v>
       </c>
       <c r="L46" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M46" s="3">
         <v>100</v>
@@ -3956,14 +4058,14 @@
         <v>100</v>
       </c>
       <c r="P46" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q46" s="3">
         <v>200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>300</v>
       </c>
-      <c r="R46" s="3">
-        <v>0</v>
-      </c>
       <c r="S46" s="3">
         <v>0</v>
       </c>
@@ -4009,8 +4111,11 @@
       <c r="AG46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4020,14 +4125,14 @@
       <c r="E47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F47" s="3">
-        <v>0</v>
+      <c r="F47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G47" s="3">
         <v>0</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>4</v>
+      <c r="H47" s="3">
+        <v>0</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>4</v>
@@ -4041,8 +4146,8 @@
       <c r="L47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -4104,8 +4209,11 @@
       <c r="AG47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4145,8 +4253,8 @@
       <c r="O48" s="3">
         <v>0</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>4</v>
+      <c r="P48" s="3">
+        <v>0</v>
       </c>
       <c r="Q48" s="3" t="s">
         <v>4</v>
@@ -4160,8 +4268,8 @@
       <c r="T48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U48" s="3">
-        <v>0</v>
+      <c r="U48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V48" s="3">
         <v>0</v>
@@ -4199,8 +4307,11 @@
       <c r="AG48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4294,8 +4405,11 @@
       <c r="AG49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4389,8 +4503,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4484,8 +4601,11 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4579,8 +4699,11 @@
       <c r="AG52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4674,28 +4797,31 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>200</v>
+      </c>
+      <c r="E54" s="3">
         <v>100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>100</v>
-      </c>
-      <c r="G54" s="3">
-        <v>200</v>
       </c>
       <c r="H54" s="3">
         <v>200</v>
       </c>
       <c r="I54" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="J54" s="3">
         <v>0</v>
@@ -4704,7 +4830,7 @@
         <v>0</v>
       </c>
       <c r="L54" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M54" s="3">
         <v>100</v>
@@ -4716,14 +4842,14 @@
         <v>100</v>
       </c>
       <c r="P54" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q54" s="3">
         <v>200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>300</v>
       </c>
-      <c r="R54" s="3">
-        <v>0</v>
-      </c>
       <c r="S54" s="3">
         <v>0</v>
       </c>
@@ -4769,8 +4895,11 @@
       <c r="AG54" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH54" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4804,8 +4933,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4839,8 +4969,9 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4848,10 +4979,10 @@
         <v>0</v>
       </c>
       <c r="E57" s="3">
+        <v>0</v>
+      </c>
+      <c r="F57" s="3">
         <v>100</v>
-      </c>
-      <c r="F57" s="3">
-        <v>200</v>
       </c>
       <c r="G57" s="3">
         <v>200</v>
@@ -4863,10 +4994,10 @@
         <v>200</v>
       </c>
       <c r="J57" s="3">
+        <v>200</v>
+      </c>
+      <c r="K57" s="3">
         <v>300</v>
-      </c>
-      <c r="K57" s="3">
-        <v>200</v>
       </c>
       <c r="L57" s="3">
         <v>200</v>
@@ -4875,13 +5006,13 @@
         <v>200</v>
       </c>
       <c r="N57" s="3">
+        <v>200</v>
+      </c>
+      <c r="O57" s="3">
         <v>100</v>
       </c>
-      <c r="O57" s="3">
-        <v>0</v>
-      </c>
-      <c r="P57" s="3" t="s">
-        <v>4</v>
+      <c r="P57" s="3">
+        <v>0</v>
       </c>
       <c r="Q57" s="3" t="s">
         <v>4</v>
@@ -4895,8 +5026,8 @@
       <c r="T57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U57" s="3">
-        <v>0</v>
+      <c r="U57" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V57" s="3">
         <v>0</v>
@@ -4922,20 +5053,23 @@
       <c r="AC57" s="3">
         <v>0</v>
       </c>
-      <c r="AD57" s="3" t="s">
-        <v>4</v>
+      <c r="AD57" s="3">
+        <v>0</v>
       </c>
       <c r="AE57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AF57" s="3">
-        <v>0</v>
+      <c r="AF57" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AG57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5029,8 +5163,11 @@
       <c r="AG58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5065,22 +5202,22 @@
         <v>600</v>
       </c>
       <c r="N59" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="O59" s="3">
         <v>700</v>
       </c>
       <c r="P59" s="3">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="Q59" s="3">
         <v>500</v>
       </c>
       <c r="R59" s="3">
+        <v>500</v>
+      </c>
+      <c r="S59" s="3">
         <v>200</v>
-      </c>
-      <c r="S59" s="3">
-        <v>100</v>
       </c>
       <c r="T59" s="3">
         <v>100</v>
@@ -5089,22 +5226,22 @@
         <v>100</v>
       </c>
       <c r="V59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W59" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="X59" s="3">
         <v>300</v>
       </c>
       <c r="Y59" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="Z59" s="3">
         <v>100</v>
       </c>
       <c r="AA59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB59" s="3">
         <v>0</v>
@@ -5124,8 +5261,11 @@
       <c r="AG59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5133,10 +5273,10 @@
         <v>600</v>
       </c>
       <c r="E60" s="3">
+        <v>600</v>
+      </c>
+      <c r="F60" s="3">
         <v>700</v>
-      </c>
-      <c r="F60" s="3">
-        <v>800</v>
       </c>
       <c r="G60" s="3">
         <v>800</v>
@@ -5157,25 +5297,25 @@
         <v>800</v>
       </c>
       <c r="M60" s="3">
+        <v>800</v>
+      </c>
+      <c r="N60" s="3">
         <v>700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>700</v>
-      </c>
-      <c r="P60" s="3">
-        <v>500</v>
       </c>
       <c r="Q60" s="3">
         <v>500</v>
       </c>
       <c r="R60" s="3">
+        <v>500</v>
+      </c>
+      <c r="S60" s="3">
         <v>200</v>
-      </c>
-      <c r="S60" s="3">
-        <v>100</v>
       </c>
       <c r="T60" s="3">
         <v>100</v>
@@ -5184,16 +5324,16 @@
         <v>100</v>
       </c>
       <c r="V60" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W60" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="X60" s="3">
         <v>300</v>
       </c>
       <c r="Y60" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="Z60" s="3">
         <v>100</v>
@@ -5205,7 +5345,7 @@
         <v>100</v>
       </c>
       <c r="AC60" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AD60" s="3">
         <v>0</v>
@@ -5219,8 +5359,11 @@
       <c r="AG60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5314,8 +5457,11 @@
       <c r="AG61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5409,8 +5555,11 @@
       <c r="AG62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5504,8 +5653,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5599,8 +5751,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5694,8 +5849,11 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -5703,10 +5861,10 @@
         <v>600</v>
       </c>
       <c r="E66" s="3">
+        <v>600</v>
+      </c>
+      <c r="F66" s="3">
         <v>700</v>
-      </c>
-      <c r="F66" s="3">
-        <v>800</v>
       </c>
       <c r="G66" s="3">
         <v>800</v>
@@ -5727,25 +5885,25 @@
         <v>800</v>
       </c>
       <c r="M66" s="3">
+        <v>800</v>
+      </c>
+      <c r="N66" s="3">
         <v>700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>700</v>
-      </c>
-      <c r="P66" s="3">
-        <v>500</v>
       </c>
       <c r="Q66" s="3">
         <v>500</v>
       </c>
       <c r="R66" s="3">
+        <v>500</v>
+      </c>
+      <c r="S66" s="3">
         <v>200</v>
-      </c>
-      <c r="S66" s="3">
-        <v>100</v>
       </c>
       <c r="T66" s="3">
         <v>100</v>
@@ -5754,16 +5912,16 @@
         <v>100</v>
       </c>
       <c r="V66" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W66" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="X66" s="3">
         <v>300</v>
       </c>
       <c r="Y66" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="Z66" s="3">
         <v>100</v>
@@ -5775,7 +5933,7 @@
         <v>100</v>
       </c>
       <c r="AC66" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AD66" s="3">
         <v>0</v>
@@ -5789,8 +5947,11 @@
       <c r="AG66" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH66" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5824,8 +5985,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5919,8 +6081,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6014,8 +6179,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6109,8 +6277,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6204,76 +6375,79 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-1200</v>
+        <v>-1300</v>
       </c>
       <c r="E72" s="3">
         <v>-1200</v>
       </c>
       <c r="F72" s="3">
-        <v>-1300</v>
+        <v>-1200</v>
       </c>
       <c r="G72" s="3">
         <v>-1300</v>
       </c>
       <c r="H72" s="3">
-        <v>-1200</v>
+        <v>-1300</v>
       </c>
       <c r="I72" s="3">
         <v>-1200</v>
       </c>
       <c r="J72" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="K72" s="3">
         <v>-1300</v>
-      </c>
-      <c r="K72" s="3">
-        <v>-1200</v>
       </c>
       <c r="L72" s="3">
         <v>-1200</v>
       </c>
       <c r="M72" s="3">
-        <v>-1100</v>
+        <v>-1200</v>
       </c>
       <c r="N72" s="3">
         <v>-1100</v>
       </c>
       <c r="O72" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="P72" s="3">
         <v>-1000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-700</v>
-      </c>
-      <c r="Q72" s="3">
-        <v>-600</v>
       </c>
       <c r="R72" s="3">
         <v>-600</v>
       </c>
       <c r="S72" s="3">
-        <v>-500</v>
+        <v>-600</v>
       </c>
       <c r="T72" s="3">
         <v>-500</v>
       </c>
       <c r="U72" s="3">
+        <v>-500</v>
+      </c>
+      <c r="V72" s="3">
         <v>-200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-100</v>
-      </c>
-      <c r="W72" s="3">
-        <v>-400</v>
       </c>
       <c r="X72" s="3">
         <v>-400</v>
       </c>
       <c r="Y72" s="3">
-        <v>-100</v>
+        <v>-400</v>
       </c>
       <c r="Z72" s="3">
         <v>-100</v>
@@ -6285,7 +6459,7 @@
         <v>-100</v>
       </c>
       <c r="AC72" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AD72" s="3">
         <v>0</v>
@@ -6299,8 +6473,11 @@
       <c r="AG72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6394,8 +6571,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6489,8 +6669,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6584,8 +6767,11 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
@@ -6596,16 +6782,16 @@
         <v>-500</v>
       </c>
       <c r="F76" s="3">
+        <v>-500</v>
+      </c>
+      <c r="G76" s="3">
         <v>-700</v>
-      </c>
-      <c r="G76" s="3">
-        <v>-600</v>
       </c>
       <c r="H76" s="3">
         <v>-600</v>
       </c>
       <c r="I76" s="3">
-        <v>-800</v>
+        <v>-600</v>
       </c>
       <c r="J76" s="3">
         <v>-800</v>
@@ -6614,7 +6800,7 @@
         <v>-800</v>
       </c>
       <c r="L76" s="3">
-        <v>-700</v>
+        <v>-800</v>
       </c>
       <c r="M76" s="3">
         <v>-700</v>
@@ -6623,19 +6809,19 @@
         <v>-700</v>
       </c>
       <c r="O76" s="3">
+        <v>-700</v>
+      </c>
+      <c r="P76" s="3">
         <v>-600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-300</v>
-      </c>
-      <c r="Q76" s="3">
-        <v>-200</v>
       </c>
       <c r="R76" s="3">
         <v>-200</v>
       </c>
       <c r="S76" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="T76" s="3">
         <v>-100</v>
@@ -6644,16 +6830,16 @@
         <v>-100</v>
       </c>
       <c r="V76" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="W76" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="X76" s="3">
         <v>-300</v>
       </c>
       <c r="Y76" s="3">
-        <v>-100</v>
+        <v>-300</v>
       </c>
       <c r="Z76" s="3">
         <v>-100</v>
@@ -6665,7 +6851,7 @@
         <v>-100</v>
       </c>
       <c r="AC76" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AD76" s="3">
         <v>0</v>
@@ -6679,8 +6865,11 @@
       <c r="AG76" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH76" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6774,108 +6963,114 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44135</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44043</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43951</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43861</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43769</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43677</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43585</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43496</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43404</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43312</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43220</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43131</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43039</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42947</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42855</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42766</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42674</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42582</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -6883,11 +7078,11 @@
         <v>-100</v>
       </c>
       <c r="E81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F81" s="3">
         <v>100</v>
       </c>
-      <c r="F81" s="3">
-        <v>0</v>
-      </c>
       <c r="G81" s="3">
         <v>0</v>
       </c>
@@ -6895,34 +7090,34 @@
         <v>0</v>
       </c>
       <c r="I81" s="3">
+        <v>0</v>
+      </c>
+      <c r="J81" s="3">
         <v>100</v>
       </c>
-      <c r="J81" s="3">
-        <v>0</v>
-      </c>
       <c r="K81" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L81" s="3">
         <v>-100</v>
       </c>
       <c r="M81" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="N81" s="3">
         <v>0</v>
       </c>
       <c r="O81" s="3">
+        <v>0</v>
+      </c>
+      <c r="P81" s="3">
         <v>-300</v>
-      </c>
-      <c r="P81" s="3">
-        <v>-100</v>
       </c>
       <c r="Q81" s="3">
         <v>-100</v>
       </c>
       <c r="R81" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="S81" s="3">
         <v>0</v>
@@ -6931,31 +7126,31 @@
         <v>0</v>
       </c>
       <c r="U81" s="3">
+        <v>0</v>
+      </c>
+      <c r="V81" s="3">
         <v>-400</v>
       </c>
-      <c r="V81" s="3">
-        <v>0</v>
-      </c>
       <c r="W81" s="3">
         <v>0</v>
       </c>
       <c r="X81" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y81" s="3">
         <v>-200</v>
       </c>
-      <c r="Y81" s="3">
-        <v>0</v>
-      </c>
       <c r="Z81" s="3">
         <v>0</v>
       </c>
       <c r="AA81" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AB81" s="3">
         <v>-100</v>
       </c>
       <c r="AC81" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AD81" s="3">
         <v>0</v>
@@ -6969,8 +7164,11 @@
       <c r="AG81" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7004,16 +7202,17 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E83" s="3">
-        <v>0</v>
+      <c r="E83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F83" s="3">
         <v>0</v>
@@ -7042,8 +7241,8 @@
       <c r="N83" s="3">
         <v>0</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>4</v>
+      <c r="O83" s="3">
+        <v>0</v>
       </c>
       <c r="P83" s="3" t="s">
         <v>4</v>
@@ -7057,8 +7256,8 @@
       <c r="S83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T83" s="3">
-        <v>0</v>
+      <c r="T83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U83" s="3">
         <v>0</v>
@@ -7099,8 +7298,11 @@
       <c r="AG83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7194,8 +7396,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7289,8 +7494,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7384,8 +7592,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7479,8 +7690,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7574,13 +7788,16 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="E89" s="3">
         <v>0</v>
@@ -7589,11 +7806,11 @@
         <v>0</v>
       </c>
       <c r="G89" s="3">
+        <v>0</v>
+      </c>
+      <c r="H89" s="3">
         <v>-100</v>
       </c>
-      <c r="H89" s="3">
-        <v>0</v>
-      </c>
       <c r="I89" s="3">
         <v>0</v>
       </c>
@@ -7613,20 +7830,20 @@
         <v>0</v>
       </c>
       <c r="O89" s="3">
+        <v>0</v>
+      </c>
+      <c r="P89" s="3">
         <v>-300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-100</v>
       </c>
-      <c r="Q89" s="3">
-        <v>0</v>
-      </c>
       <c r="R89" s="3">
+        <v>0</v>
+      </c>
+      <c r="S89" s="3">
         <v>-100</v>
       </c>
-      <c r="S89" s="3">
-        <v>0</v>
-      </c>
       <c r="T89" s="3">
         <v>0</v>
       </c>
@@ -7634,23 +7851,23 @@
         <v>0</v>
       </c>
       <c r="V89" s="3">
+        <v>0</v>
+      </c>
+      <c r="W89" s="3">
         <v>300</v>
       </c>
-      <c r="W89" s="3">
-        <v>0</v>
-      </c>
       <c r="X89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y89" s="3">
         <v>-200</v>
       </c>
-      <c r="Y89" s="3">
-        <v>0</v>
-      </c>
       <c r="Z89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA89" s="3">
         <v>-100</v>
       </c>
-      <c r="AA89" s="3">
-        <v>0</v>
-      </c>
       <c r="AB89" s="3">
         <v>0</v>
       </c>
@@ -7669,8 +7886,11 @@
       <c r="AG89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7704,8 +7924,9 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7799,8 +8020,11 @@
       <c r="AG91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7894,8 +8118,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7989,8 +8216,11 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8000,29 +8230,29 @@
       <c r="E94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3" t="s">
-        <v>4</v>
+      <c r="F94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G94" s="3">
+        <v>0</v>
       </c>
       <c r="H94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I94" s="3">
-        <v>0</v>
+      <c r="I94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J94" s="3">
         <v>0</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>4</v>
+      <c r="K94" s="3">
+        <v>0</v>
       </c>
       <c r="L94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
+      <c r="M94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N94" s="3">
         <v>0</v>
@@ -8084,8 +8314,11 @@
       <c r="AG94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8119,8 +8352,9 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8214,8 +8448,11 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8309,8 +8546,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8404,8 +8644,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8499,13 +8742,16 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E100" s="3">
         <v>0</v>
@@ -8517,11 +8763,11 @@
         <v>0</v>
       </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>200</v>
       </c>
-      <c r="I100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J100" s="3" t="s">
         <v>4</v>
       </c>
@@ -8531,27 +8777,27 @@
       <c r="L100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
+      <c r="M100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N100" s="3">
         <v>0</v>
       </c>
       <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>200</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>100</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
       <c r="T100" s="3">
         <v>0</v>
       </c>
@@ -8565,17 +8811,17 @@
         <v>0</v>
       </c>
       <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3">
         <v>200</v>
       </c>
-      <c r="Y100" s="3">
-        <v>0</v>
-      </c>
       <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="3">
         <v>100</v>
       </c>
-      <c r="AA100" s="3">
-        <v>0</v>
-      </c>
       <c r="AB100" s="3">
         <v>0</v>
       </c>
@@ -8594,8 +8840,11 @@
       <c r="AG100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8689,8 +8938,11 @@
       <c r="AG101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -8704,14 +8956,14 @@
         <v>0</v>
       </c>
       <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
         <v>-100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>200</v>
       </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
       <c r="J102" s="3">
         <v>0</v>
       </c>
@@ -8728,17 +8980,17 @@
         <v>0</v>
       </c>
       <c r="O102" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="P102" s="3">
         <v>-100</v>
       </c>
       <c r="Q102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="R102" s="3">
         <v>300</v>
       </c>
-      <c r="R102" s="3">
-        <v>0</v>
-      </c>
       <c r="S102" s="3">
         <v>0</v>
       </c>
@@ -8782,6 +9034,9 @@
         <v>0</v>
       </c>
       <c r="AG102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SNTW_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SNTW_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="92">
   <si>
     <t>SNTW</t>
   </si>
@@ -656,153 +656,157 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44135</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44043</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43951</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43861</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43769</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43677</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43585</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43496</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43404</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43312</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43220</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43131</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43039</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42947</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42855</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42766</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42674</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42582</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>4</v>
+      <c r="D8" s="3">
+        <v>100</v>
       </c>
       <c r="E8" s="3">
         <v>0</v>
@@ -810,14 +814,14 @@
       <c r="F8" s="3">
         <v>0</v>
       </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3">
-        <v>0</v>
-      </c>
-      <c r="I8" s="3">
-        <v>0</v>
+      <c r="G8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J8" s="3">
         <v>0</v>
@@ -894,13 +898,16 @@
       <c r="AH8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>4</v>
+      <c r="D9" s="3">
+        <v>0</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>4</v>
@@ -980,8 +987,8 @@
       <c r="AD9" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE9" s="3">
-        <v>0</v>
+      <c r="AE9" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AF9" s="3">
         <v>0</v>
@@ -992,13 +999,16 @@
       <c r="AH9" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI9" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>4</v>
+      <c r="D10" s="3">
+        <v>100</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>4</v>
@@ -1078,8 +1088,8 @@
       <c r="AD10" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE10" s="3">
-        <v>0</v>
+      <c r="AE10" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AF10" s="3">
         <v>0</v>
@@ -1090,8 +1100,11 @@
       <c r="AH10" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI10" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1126,8 +1139,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1224,8 +1238,11 @@
       <c r="AH12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1322,8 +1339,11 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1333,23 +1353,23 @@
       <c r="E14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G14" s="3">
         <v>-200</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H14" s="3" t="s">
         <v>4</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>4</v>
+      <c r="J14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K14" s="3">
+        <v>0</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>4</v>
@@ -1357,39 +1377,39 @@
       <c r="M14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O14" s="3">
         <v>-100</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P14" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>4</v>
+      <c r="R14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S14" s="3">
+        <v>0</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="U14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>300</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>-300</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1399,8 +1419,8 @@
       <c r="AA14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
+      <c r="AB14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AC14" s="3">
         <v>0</v>
@@ -1420,8 +1440,11 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1518,8 +1541,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1551,58 +1577,59 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E17" s="3">
         <v>100</v>
       </c>
       <c r="F17" s="3">
+        <v>100</v>
+      </c>
+      <c r="G17" s="3">
         <v>-100</v>
       </c>
-      <c r="G17" s="3">
-        <v>0</v>
-      </c>
       <c r="H17" s="3">
+        <v>0</v>
+      </c>
+      <c r="I17" s="3">
         <v>100</v>
       </c>
-      <c r="I17" s="3">
-        <v>0</v>
-      </c>
       <c r="J17" s="3">
+        <v>0</v>
+      </c>
+      <c r="K17" s="3">
         <v>-100</v>
       </c>
-      <c r="K17" s="3">
-        <v>0</v>
-      </c>
       <c r="L17" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M17" s="3">
         <v>100</v>
       </c>
       <c r="N17" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O17" s="3">
         <v>0</v>
       </c>
       <c r="P17" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="3">
         <v>300</v>
-      </c>
-      <c r="Q17" s="3">
-        <v>100</v>
       </c>
       <c r="R17" s="3">
         <v>100</v>
       </c>
       <c r="S17" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T17" s="3">
         <v>0</v>
@@ -1611,31 +1638,31 @@
         <v>0</v>
       </c>
       <c r="V17" s="3">
+        <v>0</v>
+      </c>
+      <c r="W17" s="3">
         <v>400</v>
       </c>
-      <c r="W17" s="3">
-        <v>0</v>
-      </c>
       <c r="X17" s="3">
         <v>0</v>
       </c>
       <c r="Y17" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z17" s="3">
         <v>200</v>
       </c>
-      <c r="Z17" s="3">
-        <v>0</v>
-      </c>
       <c r="AA17" s="3">
         <v>0</v>
       </c>
       <c r="AB17" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AC17" s="3">
         <v>100</v>
       </c>
       <c r="AD17" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AE17" s="3">
         <v>0</v>
@@ -1649,58 +1676,61 @@
       <c r="AH17" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>4</v>
+      <c r="D18" s="3">
+        <v>-100</v>
       </c>
       <c r="E18" s="3">
         <v>-100</v>
       </c>
       <c r="F18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J18" s="3">
+        <v>0</v>
+      </c>
+      <c r="K18" s="3">
         <v>100</v>
       </c>
-      <c r="G18" s="3">
-        <v>0</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-100</v>
-      </c>
-      <c r="I18" s="3">
-        <v>0</v>
-      </c>
-      <c r="J18" s="3">
-        <v>100</v>
-      </c>
-      <c r="K18" s="3">
-        <v>0</v>
-      </c>
       <c r="L18" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M18" s="3">
         <v>-100</v>
       </c>
       <c r="N18" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="O18" s="3">
         <v>0</v>
       </c>
       <c r="P18" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="3">
         <v>-300</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>-100</v>
       </c>
       <c r="R18" s="3">
         <v>-100</v>
       </c>
       <c r="S18" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="T18" s="3">
         <v>0</v>
@@ -1709,31 +1739,31 @@
         <v>0</v>
       </c>
       <c r="V18" s="3">
+        <v>0</v>
+      </c>
+      <c r="W18" s="3">
         <v>-400</v>
       </c>
-      <c r="W18" s="3">
-        <v>0</v>
-      </c>
       <c r="X18" s="3">
         <v>0</v>
       </c>
       <c r="Y18" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="3">
         <v>-200</v>
       </c>
-      <c r="Z18" s="3">
-        <v>0</v>
-      </c>
       <c r="AA18" s="3">
         <v>0</v>
       </c>
       <c r="AB18" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AC18" s="3">
         <v>-100</v>
       </c>
       <c r="AD18" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AE18" s="3">
         <v>0</v>
@@ -1747,8 +1777,11 @@
       <c r="AH18" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1783,13 +1816,14 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>4</v>
+      <c r="D20" s="3">
+        <v>0</v>
       </c>
       <c r="E20" s="3">
         <v>0</v>
@@ -1797,14 +1831,14 @@
       <c r="F20" s="3">
         <v>0</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
+      <c r="G20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J20" s="3">
         <v>0</v>
@@ -1881,49 +1915,52 @@
       <c r="AH20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>4</v>
+      <c r="D21" s="3">
+        <v>-100</v>
       </c>
       <c r="E21" s="3">
         <v>-100</v>
       </c>
       <c r="F21" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J21" s="3">
+        <v>0</v>
+      </c>
+      <c r="K21" s="3">
         <v>100</v>
       </c>
-      <c r="G21" s="3">
-        <v>0</v>
-      </c>
-      <c r="H21" s="3">
-        <v>0</v>
-      </c>
-      <c r="I21" s="3">
-        <v>0</v>
-      </c>
-      <c r="J21" s="3">
-        <v>100</v>
-      </c>
-      <c r="K21" s="3">
-        <v>0</v>
-      </c>
       <c r="L21" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M21" s="3">
         <v>-100</v>
       </c>
       <c r="N21" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="O21" s="3">
         <v>0</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>4</v>
+      <c r="P21" s="3">
+        <v>0</v>
       </c>
       <c r="Q21" s="3" t="s">
         <v>4</v>
@@ -1937,35 +1974,35 @@
       <c r="T21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U21" s="3">
-        <v>0</v>
-      </c>
-      <c r="V21" s="3" t="s">
-        <v>4</v>
+      <c r="U21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V21" s="3">
+        <v>0</v>
       </c>
       <c r="W21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X21" s="3">
-        <v>0</v>
+      <c r="X21" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y21" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z21" s="3">
         <v>-200</v>
       </c>
-      <c r="Z21" s="3">
-        <v>0</v>
-      </c>
       <c r="AA21" s="3">
         <v>0</v>
       </c>
       <c r="AB21" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AC21" s="3">
         <v>-100</v>
       </c>
       <c r="AD21" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AE21" s="3">
         <v>0</v>
@@ -1979,8 +2016,11 @@
       <c r="AH21" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI21" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2077,8 +2117,11 @@
       <c r="AH22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2089,11 +2132,11 @@
         <v>-100</v>
       </c>
       <c r="F23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G23" s="3">
         <v>100</v>
       </c>
-      <c r="G23" s="3">
-        <v>0</v>
-      </c>
       <c r="H23" s="3">
         <v>0</v>
       </c>
@@ -2101,34 +2144,34 @@
         <v>0</v>
       </c>
       <c r="J23" s="3">
+        <v>0</v>
+      </c>
+      <c r="K23" s="3">
         <v>100</v>
       </c>
-      <c r="K23" s="3">
-        <v>0</v>
-      </c>
       <c r="L23" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M23" s="3">
         <v>-100</v>
       </c>
       <c r="N23" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="O23" s="3">
         <v>0</v>
       </c>
       <c r="P23" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="3">
         <v>-300</v>
-      </c>
-      <c r="Q23" s="3">
-        <v>-100</v>
       </c>
       <c r="R23" s="3">
         <v>-100</v>
       </c>
       <c r="S23" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="T23" s="3">
         <v>0</v>
@@ -2137,31 +2180,31 @@
         <v>0</v>
       </c>
       <c r="V23" s="3">
+        <v>0</v>
+      </c>
+      <c r="W23" s="3">
         <v>-400</v>
       </c>
-      <c r="W23" s="3">
-        <v>0</v>
-      </c>
       <c r="X23" s="3">
         <v>0</v>
       </c>
       <c r="Y23" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="3">
         <v>-200</v>
       </c>
-      <c r="Z23" s="3">
-        <v>0</v>
-      </c>
       <c r="AA23" s="3">
         <v>0</v>
       </c>
       <c r="AB23" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AC23" s="3">
         <v>-100</v>
       </c>
       <c r="AD23" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AE23" s="3">
         <v>0</v>
@@ -2175,8 +2218,11 @@
       <c r="AH23" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2264,17 +2310,20 @@
       <c r="AE24" s="3">
         <v>0</v>
       </c>
-      <c r="AF24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG24" s="3">
-        <v>0</v>
+      <c r="AF24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AH24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2371,8 +2420,11 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2383,11 +2435,11 @@
         <v>-100</v>
       </c>
       <c r="F26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G26" s="3">
         <v>100</v>
       </c>
-      <c r="G26" s="3">
-        <v>0</v>
-      </c>
       <c r="H26" s="3">
         <v>0</v>
       </c>
@@ -2395,34 +2447,34 @@
         <v>0</v>
       </c>
       <c r="J26" s="3">
+        <v>0</v>
+      </c>
+      <c r="K26" s="3">
         <v>100</v>
       </c>
-      <c r="K26" s="3">
-        <v>0</v>
-      </c>
       <c r="L26" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M26" s="3">
         <v>-100</v>
       </c>
       <c r="N26" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="O26" s="3">
         <v>0</v>
       </c>
       <c r="P26" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="3">
         <v>-300</v>
-      </c>
-      <c r="Q26" s="3">
-        <v>-100</v>
       </c>
       <c r="R26" s="3">
         <v>-100</v>
       </c>
       <c r="S26" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="T26" s="3">
         <v>0</v>
@@ -2431,31 +2483,31 @@
         <v>0</v>
       </c>
       <c r="V26" s="3">
+        <v>0</v>
+      </c>
+      <c r="W26" s="3">
         <v>-400</v>
       </c>
-      <c r="W26" s="3">
-        <v>0</v>
-      </c>
       <c r="X26" s="3">
         <v>0</v>
       </c>
       <c r="Y26" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z26" s="3">
         <v>-200</v>
       </c>
-      <c r="Z26" s="3">
-        <v>0</v>
-      </c>
       <c r="AA26" s="3">
         <v>0</v>
       </c>
       <c r="AB26" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AC26" s="3">
         <v>-100</v>
       </c>
       <c r="AD26" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AE26" s="3">
         <v>0</v>
@@ -2469,8 +2521,11 @@
       <c r="AH26" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2481,11 +2536,11 @@
         <v>-100</v>
       </c>
       <c r="F27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G27" s="3">
         <v>100</v>
       </c>
-      <c r="G27" s="3">
-        <v>0</v>
-      </c>
       <c r="H27" s="3">
         <v>0</v>
       </c>
@@ -2493,34 +2548,34 @@
         <v>0</v>
       </c>
       <c r="J27" s="3">
+        <v>0</v>
+      </c>
+      <c r="K27" s="3">
         <v>100</v>
       </c>
-      <c r="K27" s="3">
-        <v>0</v>
-      </c>
       <c r="L27" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M27" s="3">
         <v>-100</v>
       </c>
       <c r="N27" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="O27" s="3">
         <v>0</v>
       </c>
       <c r="P27" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="3">
         <v>-300</v>
-      </c>
-      <c r="Q27" s="3">
-        <v>-100</v>
       </c>
       <c r="R27" s="3">
         <v>-100</v>
       </c>
       <c r="S27" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="T27" s="3">
         <v>0</v>
@@ -2529,31 +2584,31 @@
         <v>0</v>
       </c>
       <c r="V27" s="3">
+        <v>0</v>
+      </c>
+      <c r="W27" s="3">
         <v>-400</v>
       </c>
-      <c r="W27" s="3">
-        <v>0</v>
-      </c>
       <c r="X27" s="3">
         <v>0</v>
       </c>
       <c r="Y27" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z27" s="3">
         <v>-200</v>
       </c>
-      <c r="Z27" s="3">
-        <v>0</v>
-      </c>
       <c r="AA27" s="3">
         <v>0</v>
       </c>
       <c r="AB27" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AC27" s="3">
         <v>-100</v>
       </c>
       <c r="AD27" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AE27" s="3">
         <v>0</v>
@@ -2567,8 +2622,11 @@
       <c r="AH27" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2665,8 +2723,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2763,8 +2824,11 @@
       <c r="AH29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2861,8 +2925,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2959,13 +3026,16 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>4</v>
+      <c r="D32" s="3">
+        <v>0</v>
       </c>
       <c r="E32" s="3">
         <v>0</v>
@@ -2973,14 +3043,14 @@
       <c r="F32" s="3">
         <v>0</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
+      <c r="G32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J32" s="3">
         <v>0</v>
@@ -3057,8 +3127,11 @@
       <c r="AH32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3069,11 +3142,11 @@
         <v>-100</v>
       </c>
       <c r="F33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G33" s="3">
         <v>100</v>
       </c>
-      <c r="G33" s="3">
-        <v>0</v>
-      </c>
       <c r="H33" s="3">
         <v>0</v>
       </c>
@@ -3081,34 +3154,34 @@
         <v>0</v>
       </c>
       <c r="J33" s="3">
+        <v>0</v>
+      </c>
+      <c r="K33" s="3">
         <v>100</v>
       </c>
-      <c r="K33" s="3">
-        <v>0</v>
-      </c>
       <c r="L33" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M33" s="3">
         <v>-100</v>
       </c>
       <c r="N33" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="O33" s="3">
         <v>0</v>
       </c>
       <c r="P33" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="3">
         <v>-300</v>
-      </c>
-      <c r="Q33" s="3">
-        <v>-100</v>
       </c>
       <c r="R33" s="3">
         <v>-100</v>
       </c>
       <c r="S33" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="T33" s="3">
         <v>0</v>
@@ -3117,31 +3190,31 @@
         <v>0</v>
       </c>
       <c r="V33" s="3">
+        <v>0</v>
+      </c>
+      <c r="W33" s="3">
         <v>-400</v>
       </c>
-      <c r="W33" s="3">
-        <v>0</v>
-      </c>
       <c r="X33" s="3">
         <v>0</v>
       </c>
       <c r="Y33" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z33" s="3">
         <v>-200</v>
       </c>
-      <c r="Z33" s="3">
-        <v>0</v>
-      </c>
       <c r="AA33" s="3">
         <v>0</v>
       </c>
       <c r="AB33" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AC33" s="3">
         <v>-100</v>
       </c>
       <c r="AD33" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AE33" s="3">
         <v>0</v>
@@ -3155,8 +3228,11 @@
       <c r="AH33" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3253,8 +3329,11 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3265,11 +3344,11 @@
         <v>-100</v>
       </c>
       <c r="F35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G35" s="3">
         <v>100</v>
       </c>
-      <c r="G35" s="3">
-        <v>0</v>
-      </c>
       <c r="H35" s="3">
         <v>0</v>
       </c>
@@ -3277,34 +3356,34 @@
         <v>0</v>
       </c>
       <c r="J35" s="3">
+        <v>0</v>
+      </c>
+      <c r="K35" s="3">
         <v>100</v>
       </c>
-      <c r="K35" s="3">
-        <v>0</v>
-      </c>
       <c r="L35" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M35" s="3">
         <v>-100</v>
       </c>
       <c r="N35" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="O35" s="3">
         <v>0</v>
       </c>
       <c r="P35" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="3">
         <v>-300</v>
-      </c>
-      <c r="Q35" s="3">
-        <v>-100</v>
       </c>
       <c r="R35" s="3">
         <v>-100</v>
       </c>
       <c r="S35" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="T35" s="3">
         <v>0</v>
@@ -3313,31 +3392,31 @@
         <v>0</v>
       </c>
       <c r="V35" s="3">
+        <v>0</v>
+      </c>
+      <c r="W35" s="3">
         <v>-400</v>
       </c>
-      <c r="W35" s="3">
-        <v>0</v>
-      </c>
       <c r="X35" s="3">
         <v>0</v>
       </c>
       <c r="Y35" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z35" s="3">
         <v>-200</v>
       </c>
-      <c r="Z35" s="3">
-        <v>0</v>
-      </c>
       <c r="AA35" s="3">
         <v>0</v>
       </c>
       <c r="AB35" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AC35" s="3">
         <v>-100</v>
       </c>
       <c r="AD35" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AE35" s="3">
         <v>0</v>
@@ -3351,111 +3430,117 @@
       <c r="AH35" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44135</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44043</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43951</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43861</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43769</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43677</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43585</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43496</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43404</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43312</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43220</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43131</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43039</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42947</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42855</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42766</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42674</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42582</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3490,8 +3575,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3526,16 +3612,17 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>100</v>
+      </c>
+      <c r="E41" s="3">
         <v>200</v>
-      </c>
-      <c r="E41" s="3">
-        <v>100</v>
       </c>
       <c r="F41" s="3">
         <v>100</v>
@@ -3544,13 +3631,13 @@
         <v>100</v>
       </c>
       <c r="H41" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I41" s="3">
         <v>200</v>
       </c>
       <c r="J41" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K41" s="3">
         <v>0</v>
@@ -3559,7 +3646,7 @@
         <v>0</v>
       </c>
       <c r="M41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N41" s="3">
         <v>100</v>
@@ -3571,14 +3658,14 @@
         <v>100</v>
       </c>
       <c r="Q41" s="3">
+        <v>100</v>
+      </c>
+      <c r="R41" s="3">
         <v>200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>300</v>
       </c>
-      <c r="S41" s="3">
-        <v>0</v>
-      </c>
       <c r="T41" s="3">
         <v>0</v>
       </c>
@@ -3609,11 +3696,11 @@
       <c r="AC41" s="3">
         <v>0</v>
       </c>
-      <c r="AD41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE41" s="3">
-        <v>0</v>
+      <c r="AD41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE41" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AF41" s="3">
         <v>0</v>
@@ -3624,8 +3711,11 @@
       <c r="AH41" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3722,8 +3812,11 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3820,31 +3913,34 @@
       <c r="AH43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
         <v>0</v>
       </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="E44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -3918,8 +4014,11 @@
       <c r="AH44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3938,8 +4037,8 @@
       <c r="H45" s="3">
         <v>0</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>4</v>
+      <c r="I45" s="3">
+        <v>0</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>4</v>
@@ -3953,8 +4052,8 @@
       <c r="M45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N45" s="3">
-        <v>0</v>
+      <c r="N45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O45" s="3">
         <v>0</v>
@@ -3971,14 +4070,14 @@
       <c r="S45" s="3">
         <v>0</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>4</v>
+      <c r="T45" s="3">
+        <v>0</v>
       </c>
       <c r="U45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V45" s="3">
-        <v>0</v>
+      <c r="V45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W45" s="3">
         <v>0</v>
@@ -3998,11 +4097,11 @@
       <c r="AB45" s="3">
         <v>0</v>
       </c>
-      <c r="AC45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD45" s="3">
-        <v>0</v>
+      <c r="AC45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AE45" s="3">
         <v>0</v>
@@ -4016,31 +4115,34 @@
       <c r="AH45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>100</v>
+      </c>
+      <c r="E46" s="3">
         <v>200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>100</v>
-      </c>
-      <c r="H46" s="3">
-        <v>200</v>
       </c>
       <c r="I46" s="3">
         <v>200</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -4049,7 +4151,7 @@
         <v>0</v>
       </c>
       <c r="M46" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N46" s="3">
         <v>100</v>
@@ -4061,14 +4163,14 @@
         <v>100</v>
       </c>
       <c r="Q46" s="3">
+        <v>100</v>
+      </c>
+      <c r="R46" s="3">
         <v>200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>300</v>
       </c>
-      <c r="S46" s="3">
-        <v>0</v>
-      </c>
       <c r="T46" s="3">
         <v>0</v>
       </c>
@@ -4114,8 +4216,11 @@
       <c r="AH46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4128,14 +4233,14 @@
       <c r="F47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G47" s="3">
-        <v>0</v>
+      <c r="G47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H47" s="3">
         <v>0</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>4</v>
+      <c r="I47" s="3">
+        <v>0</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>4</v>
@@ -4149,8 +4254,8 @@
       <c r="M47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N47" s="3">
-        <v>0</v>
+      <c r="N47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O47" s="3">
         <v>0</v>
@@ -4212,8 +4317,11 @@
       <c r="AH47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4256,8 +4364,8 @@
       <c r="P48" s="3">
         <v>0</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>4</v>
+      <c r="Q48" s="3">
+        <v>0</v>
       </c>
       <c r="R48" s="3" t="s">
         <v>4</v>
@@ -4271,8 +4379,8 @@
       <c r="U48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V48" s="3">
-        <v>0</v>
+      <c r="V48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W48" s="3">
         <v>0</v>
@@ -4310,31 +4418,34 @@
       <c r="AH48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>0</v>
-      </c>
-      <c r="E49" s="3">
-        <v>0</v>
-      </c>
-      <c r="F49" s="3">
-        <v>0</v>
-      </c>
-      <c r="G49" s="3">
-        <v>0</v>
-      </c>
-      <c r="H49" s="3">
-        <v>0</v>
-      </c>
-      <c r="I49" s="3">
-        <v>0</v>
-      </c>
-      <c r="J49" s="3">
-        <v>0</v>
+        <v>2600</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K49" s="3">
         <v>0</v>
@@ -4408,8 +4519,11 @@
       <c r="AH49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4506,8 +4620,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4604,8 +4721,11 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4702,8 +4822,11 @@
       <c r="AH52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4800,31 +4923,34 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E54" s="3">
         <v>200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>100</v>
-      </c>
-      <c r="H54" s="3">
-        <v>200</v>
       </c>
       <c r="I54" s="3">
         <v>200</v>
       </c>
       <c r="J54" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K54" s="3">
         <v>0</v>
@@ -4833,7 +4959,7 @@
         <v>0</v>
       </c>
       <c r="M54" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N54" s="3">
         <v>100</v>
@@ -4845,14 +4971,14 @@
         <v>100</v>
       </c>
       <c r="Q54" s="3">
+        <v>100</v>
+      </c>
+      <c r="R54" s="3">
         <v>200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>300</v>
       </c>
-      <c r="S54" s="3">
-        <v>0</v>
-      </c>
       <c r="T54" s="3">
         <v>0</v>
       </c>
@@ -4898,8 +5024,11 @@
       <c r="AH54" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI54" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4934,8 +5063,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4970,8 +5100,9 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4982,10 +5113,10 @@
         <v>0</v>
       </c>
       <c r="F57" s="3">
+        <v>0</v>
+      </c>
+      <c r="G57" s="3">
         <v>100</v>
-      </c>
-      <c r="G57" s="3">
-        <v>200</v>
       </c>
       <c r="H57" s="3">
         <v>200</v>
@@ -4997,10 +5128,10 @@
         <v>200</v>
       </c>
       <c r="K57" s="3">
+        <v>200</v>
+      </c>
+      <c r="L57" s="3">
         <v>300</v>
-      </c>
-      <c r="L57" s="3">
-        <v>200</v>
       </c>
       <c r="M57" s="3">
         <v>200</v>
@@ -5009,13 +5140,13 @@
         <v>200</v>
       </c>
       <c r="O57" s="3">
+        <v>200</v>
+      </c>
+      <c r="P57" s="3">
         <v>100</v>
       </c>
-      <c r="P57" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q57" s="3" t="s">
-        <v>4</v>
+      <c r="Q57" s="3">
+        <v>0</v>
       </c>
       <c r="R57" s="3" t="s">
         <v>4</v>
@@ -5029,8 +5160,8 @@
       <c r="U57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V57" s="3">
-        <v>0</v>
+      <c r="V57" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W57" s="3">
         <v>0</v>
@@ -5056,20 +5187,23 @@
       <c r="AD57" s="3">
         <v>0</v>
       </c>
-      <c r="AE57" s="3" t="s">
-        <v>4</v>
+      <c r="AE57" s="3">
+        <v>0</v>
       </c>
       <c r="AF57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AG57" s="3">
-        <v>0</v>
+      <c r="AG57" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AH57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5166,13 +5300,16 @@
       <c r="AH58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="E59" s="3">
         <v>600</v>
@@ -5205,22 +5342,22 @@
         <v>600</v>
       </c>
       <c r="O59" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="P59" s="3">
         <v>700</v>
       </c>
       <c r="Q59" s="3">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="R59" s="3">
         <v>500</v>
       </c>
       <c r="S59" s="3">
+        <v>500</v>
+      </c>
+      <c r="T59" s="3">
         <v>200</v>
-      </c>
-      <c r="T59" s="3">
-        <v>100</v>
       </c>
       <c r="U59" s="3">
         <v>100</v>
@@ -5229,22 +5366,22 @@
         <v>100</v>
       </c>
       <c r="W59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X59" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="Y59" s="3">
         <v>300</v>
       </c>
       <c r="Z59" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="AA59" s="3">
         <v>100</v>
       </c>
       <c r="AB59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC59" s="3">
         <v>0</v>
@@ -5264,22 +5401,25 @@
       <c r="AH59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="E60" s="3">
         <v>600</v>
       </c>
       <c r="F60" s="3">
+        <v>600</v>
+      </c>
+      <c r="G60" s="3">
         <v>700</v>
-      </c>
-      <c r="G60" s="3">
-        <v>800</v>
       </c>
       <c r="H60" s="3">
         <v>800</v>
@@ -5300,25 +5440,25 @@
         <v>800</v>
       </c>
       <c r="N60" s="3">
+        <v>800</v>
+      </c>
+      <c r="O60" s="3">
         <v>700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>700</v>
-      </c>
-      <c r="Q60" s="3">
-        <v>500</v>
       </c>
       <c r="R60" s="3">
         <v>500</v>
       </c>
       <c r="S60" s="3">
+        <v>500</v>
+      </c>
+      <c r="T60" s="3">
         <v>200</v>
-      </c>
-      <c r="T60" s="3">
-        <v>100</v>
       </c>
       <c r="U60" s="3">
         <v>100</v>
@@ -5327,16 +5467,16 @@
         <v>100</v>
       </c>
       <c r="W60" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X60" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="Y60" s="3">
         <v>300</v>
       </c>
       <c r="Z60" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="AA60" s="3">
         <v>100</v>
@@ -5348,7 +5488,7 @@
         <v>100</v>
       </c>
       <c r="AD60" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AE60" s="3">
         <v>0</v>
@@ -5362,8 +5502,11 @@
       <c r="AH60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5460,8 +5603,11 @@
       <c r="AH61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5558,8 +5704,11 @@
       <c r="AH62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5656,8 +5805,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5754,8 +5906,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5852,22 +6007,25 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="E66" s="3">
         <v>600</v>
       </c>
       <c r="F66" s="3">
+        <v>600</v>
+      </c>
+      <c r="G66" s="3">
         <v>700</v>
-      </c>
-      <c r="G66" s="3">
-        <v>800</v>
       </c>
       <c r="H66" s="3">
         <v>800</v>
@@ -5888,25 +6046,25 @@
         <v>800</v>
       </c>
       <c r="N66" s="3">
+        <v>800</v>
+      </c>
+      <c r="O66" s="3">
         <v>700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>700</v>
-      </c>
-      <c r="Q66" s="3">
-        <v>500</v>
       </c>
       <c r="R66" s="3">
         <v>500</v>
       </c>
       <c r="S66" s="3">
+        <v>500</v>
+      </c>
+      <c r="T66" s="3">
         <v>200</v>
-      </c>
-      <c r="T66" s="3">
-        <v>100</v>
       </c>
       <c r="U66" s="3">
         <v>100</v>
@@ -5915,16 +6073,16 @@
         <v>100</v>
       </c>
       <c r="W66" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X66" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="Y66" s="3">
         <v>300</v>
       </c>
       <c r="Z66" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="AA66" s="3">
         <v>100</v>
@@ -5936,7 +6094,7 @@
         <v>100</v>
       </c>
       <c r="AD66" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AE66" s="3">
         <v>0</v>
@@ -5950,8 +6108,11 @@
       <c r="AH66" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI66" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5986,8 +6147,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6084,8 +6246,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6182,8 +6347,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6280,8 +6448,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6378,79 +6549,82 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1300</v>
-      </c>
-      <c r="E72" s="3">
-        <v>-1200</v>
       </c>
       <c r="F72" s="3">
         <v>-1200</v>
       </c>
       <c r="G72" s="3">
-        <v>-1300</v>
+        <v>-1200</v>
       </c>
       <c r="H72" s="3">
         <v>-1300</v>
       </c>
       <c r="I72" s="3">
-        <v>-1200</v>
+        <v>-1300</v>
       </c>
       <c r="J72" s="3">
         <v>-1200</v>
       </c>
       <c r="K72" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="L72" s="3">
         <v>-1300</v>
-      </c>
-      <c r="L72" s="3">
-        <v>-1200</v>
       </c>
       <c r="M72" s="3">
         <v>-1200</v>
       </c>
       <c r="N72" s="3">
-        <v>-1100</v>
+        <v>-1200</v>
       </c>
       <c r="O72" s="3">
         <v>-1100</v>
       </c>
       <c r="P72" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="Q72" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-700</v>
-      </c>
-      <c r="R72" s="3">
-        <v>-600</v>
       </c>
       <c r="S72" s="3">
         <v>-600</v>
       </c>
       <c r="T72" s="3">
-        <v>-500</v>
+        <v>-600</v>
       </c>
       <c r="U72" s="3">
         <v>-500</v>
       </c>
       <c r="V72" s="3">
+        <v>-500</v>
+      </c>
+      <c r="W72" s="3">
         <v>-200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-100</v>
-      </c>
-      <c r="X72" s="3">
-        <v>-400</v>
       </c>
       <c r="Y72" s="3">
         <v>-400</v>
       </c>
       <c r="Z72" s="3">
-        <v>-100</v>
+        <v>-400</v>
       </c>
       <c r="AA72" s="3">
         <v>-100</v>
@@ -6462,7 +6636,7 @@
         <v>-100</v>
       </c>
       <c r="AD72" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AE72" s="3">
         <v>0</v>
@@ -6476,8 +6650,11 @@
       <c r="AH72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6574,8 +6751,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6672,8 +6852,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6770,13 +6953,16 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>-500</v>
+        <v>2100</v>
       </c>
       <c r="E76" s="3">
         <v>-500</v>
@@ -6785,16 +6971,16 @@
         <v>-500</v>
       </c>
       <c r="G76" s="3">
+        <v>-500</v>
+      </c>
+      <c r="H76" s="3">
         <v>-700</v>
-      </c>
-      <c r="H76" s="3">
-        <v>-600</v>
       </c>
       <c r="I76" s="3">
         <v>-600</v>
       </c>
       <c r="J76" s="3">
-        <v>-800</v>
+        <v>-600</v>
       </c>
       <c r="K76" s="3">
         <v>-800</v>
@@ -6803,7 +6989,7 @@
         <v>-800</v>
       </c>
       <c r="M76" s="3">
-        <v>-700</v>
+        <v>-800</v>
       </c>
       <c r="N76" s="3">
         <v>-700</v>
@@ -6812,19 +6998,19 @@
         <v>-700</v>
       </c>
       <c r="P76" s="3">
+        <v>-700</v>
+      </c>
+      <c r="Q76" s="3">
         <v>-600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-300</v>
-      </c>
-      <c r="R76" s="3">
-        <v>-200</v>
       </c>
       <c r="S76" s="3">
         <v>-200</v>
       </c>
       <c r="T76" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="U76" s="3">
         <v>-100</v>
@@ -6833,16 +7019,16 @@
         <v>-100</v>
       </c>
       <c r="W76" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="X76" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="Y76" s="3">
         <v>-300</v>
       </c>
       <c r="Z76" s="3">
-        <v>-100</v>
+        <v>-300</v>
       </c>
       <c r="AA76" s="3">
         <v>-100</v>
@@ -6854,7 +7040,7 @@
         <v>-100</v>
       </c>
       <c r="AD76" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AE76" s="3">
         <v>0</v>
@@ -6868,8 +7054,11 @@
       <c r="AH76" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI76" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6966,111 +7155,117 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44135</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44043</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43951</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43861</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43769</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43677</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43585</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43496</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43404</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43312</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43220</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43131</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43039</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42947</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42855</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42766</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42674</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42582</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -7081,11 +7276,11 @@
         <v>-100</v>
       </c>
       <c r="F81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G81" s="3">
         <v>100</v>
       </c>
-      <c r="G81" s="3">
-        <v>0</v>
-      </c>
       <c r="H81" s="3">
         <v>0</v>
       </c>
@@ -7093,34 +7288,34 @@
         <v>0</v>
       </c>
       <c r="J81" s="3">
+        <v>0</v>
+      </c>
+      <c r="K81" s="3">
         <v>100</v>
       </c>
-      <c r="K81" s="3">
-        <v>0</v>
-      </c>
       <c r="L81" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M81" s="3">
         <v>-100</v>
       </c>
       <c r="N81" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="O81" s="3">
         <v>0</v>
       </c>
       <c r="P81" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q81" s="3">
         <v>-300</v>
-      </c>
-      <c r="Q81" s="3">
-        <v>-100</v>
       </c>
       <c r="R81" s="3">
         <v>-100</v>
       </c>
       <c r="S81" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="T81" s="3">
         <v>0</v>
@@ -7129,31 +7324,31 @@
         <v>0</v>
       </c>
       <c r="V81" s="3">
+        <v>0</v>
+      </c>
+      <c r="W81" s="3">
         <v>-400</v>
       </c>
-      <c r="W81" s="3">
-        <v>0</v>
-      </c>
       <c r="X81" s="3">
         <v>0</v>
       </c>
       <c r="Y81" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z81" s="3">
         <v>-200</v>
       </c>
-      <c r="Z81" s="3">
-        <v>0</v>
-      </c>
       <c r="AA81" s="3">
         <v>0</v>
       </c>
       <c r="AB81" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AC81" s="3">
         <v>-100</v>
       </c>
       <c r="AD81" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AE81" s="3">
         <v>0</v>
@@ -7167,8 +7362,11 @@
       <c r="AH81" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7203,8 +7401,9 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7214,8 +7413,8 @@
       <c r="E83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F83" s="3">
-        <v>0</v>
+      <c r="F83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G83" s="3">
         <v>0</v>
@@ -7244,8 +7443,8 @@
       <c r="O83" s="3">
         <v>0</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>4</v>
+      <c r="P83" s="3">
+        <v>0</v>
       </c>
       <c r="Q83" s="3" t="s">
         <v>4</v>
@@ -7259,8 +7458,8 @@
       <c r="T83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U83" s="3">
-        <v>0</v>
+      <c r="U83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V83" s="3">
         <v>0</v>
@@ -7301,8 +7500,11 @@
       <c r="AH83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7399,8 +7601,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7497,8 +7702,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7595,8 +7803,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7693,8 +7904,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7791,17 +8005,20 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>0</v>
+      </c>
+      <c r="E89" s="3">
         <v>-200</v>
       </c>
-      <c r="E89" s="3">
-        <v>0</v>
-      </c>
       <c r="F89" s="3">
         <v>0</v>
       </c>
@@ -7809,11 +8026,11 @@
         <v>0</v>
       </c>
       <c r="H89" s="3">
+        <v>0</v>
+      </c>
+      <c r="I89" s="3">
         <v>-100</v>
       </c>
-      <c r="I89" s="3">
-        <v>0</v>
-      </c>
       <c r="J89" s="3">
         <v>0</v>
       </c>
@@ -7833,20 +8050,20 @@
         <v>0</v>
       </c>
       <c r="P89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q89" s="3">
         <v>-300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-100</v>
       </c>
-      <c r="R89" s="3">
-        <v>0</v>
-      </c>
       <c r="S89" s="3">
+        <v>0</v>
+      </c>
+      <c r="T89" s="3">
         <v>-100</v>
       </c>
-      <c r="T89" s="3">
-        <v>0</v>
-      </c>
       <c r="U89" s="3">
         <v>0</v>
       </c>
@@ -7854,23 +8071,23 @@
         <v>0</v>
       </c>
       <c r="W89" s="3">
+        <v>0</v>
+      </c>
+      <c r="X89" s="3">
         <v>300</v>
       </c>
-      <c r="X89" s="3">
-        <v>0</v>
-      </c>
       <c r="Y89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z89" s="3">
         <v>-200</v>
       </c>
-      <c r="Z89" s="3">
-        <v>0</v>
-      </c>
       <c r="AA89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB89" s="3">
         <v>-100</v>
       </c>
-      <c r="AB89" s="3">
-        <v>0</v>
-      </c>
       <c r="AC89" s="3">
         <v>0</v>
       </c>
@@ -7889,8 +8106,11 @@
       <c r="AH89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7925,8 +8145,9 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8023,8 +8244,11 @@
       <c r="AH91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8121,8 +8345,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8219,13 +8446,16 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>4</v>
+      <c r="D94" s="3">
+        <v>-2700</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>4</v>
@@ -8233,29 +8463,29 @@
       <c r="F94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>4</v>
+      <c r="G94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H94" s="3">
+        <v>0</v>
       </c>
       <c r="I94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J94" s="3">
-        <v>0</v>
+      <c r="J94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K94" s="3">
         <v>0</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>4</v>
+      <c r="L94" s="3">
+        <v>0</v>
       </c>
       <c r="M94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
+      <c r="N94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O94" s="3">
         <v>0</v>
@@ -8317,8 +8547,11 @@
       <c r="AH94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8353,8 +8586,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8451,8 +8685,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8549,8 +8786,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8647,8 +8887,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8745,17 +8988,20 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E100" s="3">
         <v>200</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
       <c r="F100" s="3">
         <v>0</v>
       </c>
@@ -8766,11 +9012,11 @@
         <v>0</v>
       </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>200</v>
       </c>
-      <c r="J100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K100" s="3" t="s">
         <v>4</v>
       </c>
@@ -8780,27 +9026,27 @@
       <c r="M100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
+      <c r="N100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O100" s="3">
         <v>0</v>
       </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>200</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>100</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
       <c r="U100" s="3">
         <v>0</v>
       </c>
@@ -8814,17 +9060,17 @@
         <v>0</v>
       </c>
       <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3">
         <v>200</v>
       </c>
-      <c r="Z100" s="3">
-        <v>0</v>
-      </c>
       <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB100" s="3">
         <v>100</v>
       </c>
-      <c r="AB100" s="3">
-        <v>0</v>
-      </c>
       <c r="AC100" s="3">
         <v>0</v>
       </c>
@@ -8843,8 +9089,11 @@
       <c r="AH100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8941,8 +9190,11 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -8959,14 +9211,14 @@
         <v>0</v>
       </c>
       <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
         <v>-100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>200</v>
       </c>
-      <c r="J102" s="3">
-        <v>0</v>
-      </c>
       <c r="K102" s="3">
         <v>0</v>
       </c>
@@ -8983,17 +9235,17 @@
         <v>0</v>
       </c>
       <c r="P102" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Q102" s="3">
         <v>-100</v>
       </c>
       <c r="R102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="S102" s="3">
         <v>300</v>
       </c>
-      <c r="S102" s="3">
-        <v>0</v>
-      </c>
       <c r="T102" s="3">
         <v>0</v>
       </c>
@@ -9037,6 +9289,9 @@
         <v>0</v>
       </c>
       <c r="AH102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI102" s="3">
         <v>0</v>
       </c>
     </row>
